--- a/datos/queseria_final_tidy.xlsx
+++ b/datos/queseria_final_tidy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{3B7945C6-9DAC-46B0-AE41-EA9F33CCC2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AF88795-F7A6-4AAC-9D35-7DE133550745}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{3B7945C6-9DAC-46B0-AE41-EA9F33CCC2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB288AA8-1E1A-496B-B4F0-7E2E80FCAF1C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8B9CF080-FDD4-4586-B682-2B22866106B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{8B9CF080-FDD4-4586-B682-2B22866106B1}"/>
   </bookViews>
   <sheets>
     <sheet name="queseria_final_tidy" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -203,8 +203,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -696,7 +697,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -748,7 +749,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -781,7 +782,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -12238,7 +12239,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D938F149-C130-472B-A868-E1B9EB4C7E25}" name="TablaDinámica2" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D938F149-C130-472B-A868-E1B9EB4C7E25}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="31">
     <pivotField numFmtId="14" showAll="0">
@@ -12768,7 +12769,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E3FA40C7-9679-4AAD-A715-2CDFF68B3C50}" name="TablaDinámica2" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E3FA40C7-9679-4AAD-A715-2CDFF68B3C50}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="31">
     <pivotField numFmtId="14" showAll="0">
@@ -13301,7 +13302,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{824C0C17-8164-4471-AD43-74C17C79B417}" name="Tabla1" displayName="Tabla1" ref="A1:AB365" totalsRowShown="0">
   <autoFilter ref="A1:AB365" xr:uid="{824C0C17-8164-4471-AD43-74C17C79B417}"/>
   <tableColumns count="28">
-    <tableColumn id="1" xr3:uid="{99A0AE4C-39DD-400F-9F23-11CE96BF9E3F}" name="fecha" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{99A0AE4C-39DD-400F-9F23-11CE96BF9E3F}" name="fecha" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{411A109F-AD82-48BE-8350-D61F83D41937}" name="entrada_kg"/>
     <tableColumn id="3" xr3:uid="{C69C38D1-6673-4E9F-BC17-D7833BFA90F5}" name="entrada_litros"/>
     <tableColumn id="4" xr3:uid="{B6E5C5FF-909C-4581-8F09-5A4E147B48B0}" name="entrada_grasa_g_l"/>
@@ -13317,38 +13318,38 @@
     <tableColumn id="23" xr3:uid="{F403A714-1800-4D26-9AF1-B6655B816C60}" name="suero_grasa_g_l"/>
     <tableColumn id="22" xr3:uid="{F53BCEFE-F638-4DCC-9C89-95E955DE1BC1}" name="suero_prot_g_l"/>
     <tableColumn id="21" xr3:uid="{A6C9938E-0AA2-4E29-A8DC-F754989BB147}" name="suero_est_g_l"/>
-    <tableColumn id="13" xr3:uid="{BA3D3A7D-98AE-465A-A04F-EAFDC5620F57}" name="entrada_grasa_kg" dataDxfId="12">
+    <tableColumn id="13" xr3:uid="{BA3D3A7D-98AE-465A-A04F-EAFDC5620F57}" name="entrada_grasa_kg" dataDxfId="11">
       <calculatedColumnFormula>Tabla1[[#This Row],[entrada_litros]]*Tabla1[[#This Row],[entrada_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{ECAB9C49-9B80-4690-BDFB-33A5C9A5855F}" name="entrada_prot_kg" dataDxfId="11">
+    <tableColumn id="14" xr3:uid="{ECAB9C49-9B80-4690-BDFB-33A5C9A5855F}" name="entrada_prot_kg" dataDxfId="10">
       <calculatedColumnFormula>Tabla1[[#This Row],[entrada_prot_g_l]]*Tabla1[[#This Row],[entrada_litros]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{3884887A-AFCB-466C-8516-33532C44D81A}" name="cuba_fab_grasa_kg" dataDxfId="10">
+    <tableColumn id="15" xr3:uid="{3884887A-AFCB-466C-8516-33532C44D81A}" name="cuba_fab_grasa_kg" dataDxfId="9">
       <calculatedColumnFormula>Tabla1[[#This Row],[cuba_fab_litros]]*Tabla1[[#This Row],[cuba_fab_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{FE93E448-E7E3-4BAA-A21E-1C868C969B6B}" name="cuba_fab_prot_kg" dataDxfId="9">
+    <tableColumn id="16" xr3:uid="{FE93E448-E7E3-4BAA-A21E-1C868C969B6B}" name="cuba_fab_prot_kg" dataDxfId="8">
       <calculatedColumnFormula>Tabla1[[#This Row],[cuba_fab_litros]]*Tabla1[[#This Row],[cuba_fab_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{9E87A0D2-96E2-47CF-A557-DE77F5489569}" name="queso_est_kg" dataDxfId="8">
+    <tableColumn id="17" xr3:uid="{9E87A0D2-96E2-47CF-A557-DE77F5489569}" name="queso_est_kg" dataDxfId="7">
       <calculatedColumnFormula>Tabla1[[#This Row],[queso_kg]]*Tabla1[[#This Row],[queso_est_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{7D142DE3-472E-4628-8F12-4F8CCEE02A8D}" name="queso_mg_kg" dataDxfId="7">
+    <tableColumn id="18" xr3:uid="{7D142DE3-472E-4628-8F12-4F8CCEE02A8D}" name="queso_mg_kg" dataDxfId="6">
       <calculatedColumnFormula>Tabla1[[#This Row],[queso_kg]]*Tabla1[[#This Row],[queso_mg_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{94A6B5A5-9CA4-4778-871F-EF1623A78A57}" name="queso_esm_kg" dataDxfId="0">
+    <tableColumn id="28" xr3:uid="{94A6B5A5-9CA4-4778-871F-EF1623A78A57}" name="queso_esm_kg" dataDxfId="5">
       <calculatedColumnFormula>Tabla1[[#This Row],[queso_est_kg]]-Tabla1[[#This Row],[queso_mg_kg]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{F125589E-13AA-49C5-84DE-A9D2D30D2458}" name="semanaISO" dataDxfId="6">
+    <tableColumn id="19" xr3:uid="{F125589E-13AA-49C5-84DE-A9D2D30D2458}" name="semanaISO" dataDxfId="4">
       <calculatedColumnFormula>_xlfn.ISOWEEKNUM(Tabla1[[#This Row],[fecha]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{3F3CA61F-0914-466B-ADEE-F97130995988}" name="semana" dataDxfId="5"/>
-    <tableColumn id="25" xr3:uid="{7DAA0C24-AC27-4679-9182-5C0CF0D093DC}" name="suero_grasa_kg" dataDxfId="4">
+    <tableColumn id="20" xr3:uid="{3F3CA61F-0914-466B-ADEE-F97130995988}" name="semana" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{7DAA0C24-AC27-4679-9182-5C0CF0D093DC}" name="suero_grasa_kg" dataDxfId="2">
       <calculatedColumnFormula>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{4F813244-B392-498C-AC21-D5594D817434}" name="suero_prot_kg" dataDxfId="3">
+    <tableColumn id="26" xr3:uid="{4F813244-B392-498C-AC21-D5594D817434}" name="suero_prot_kg" dataDxfId="1">
       <calculatedColumnFormula>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{762D5A61-6B33-44ED-82E3-B3CCEF350561}" name="suero_est_kg" dataDxfId="2">
+    <tableColumn id="27" xr3:uid="{762D5A61-6B33-44ED-82E3-B3CCEF350561}" name="suero_est_kg" dataDxfId="0">
       <calculatedColumnFormula>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13859,15 +13860,15 @@
       <c r="Y2">
         <v>1</v>
       </c>
-      <c r="Z2" s="7">
+      <c r="Z2">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA2" s="7">
+      <c r="AA2">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB2" s="7">
+      <c r="AB2">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -13956,15 +13957,15 @@
       <c r="Y3">
         <v>1</v>
       </c>
-      <c r="Z3" s="7">
+      <c r="Z3">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.746149999999993</v>
       </c>
-      <c r="AA3" s="7">
+      <c r="AA3">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.090319999999998</v>
       </c>
-      <c r="AB3" s="7">
+      <c r="AB3">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>298.08291000000003</v>
       </c>
@@ -14053,15 +14054,15 @@
       <c r="Y4">
         <v>1</v>
       </c>
-      <c r="Z4" s="7">
+      <c r="Z4">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.408639999999998</v>
       </c>
-      <c r="AA4" s="7">
+      <c r="AA4">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.703199999999995</v>
       </c>
-      <c r="AB4" s="7">
+      <c r="AB4">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>296.81135999999998</v>
       </c>
@@ -14150,15 +14151,15 @@
       <c r="Y5">
         <v>1</v>
       </c>
-      <c r="Z5" s="7">
+      <c r="Z5">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.213940000000001</v>
       </c>
-      <c r="AA5" s="7">
+      <c r="AA5">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>37.591759999999994</v>
       </c>
-      <c r="AB5" s="7">
+      <c r="AB5">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.18239999999997</v>
       </c>
@@ -14247,15 +14248,15 @@
       <c r="Y6">
         <v>1</v>
       </c>
-      <c r="Z6" s="7">
+      <c r="Z6">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.843259999999997</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AA6">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>35.485680000000002</v>
       </c>
-      <c r="AB6" s="7">
+      <c r="AB6">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.84602000000001</v>
       </c>
@@ -14344,15 +14345,15 @@
       <c r="Y7">
         <v>1</v>
       </c>
-      <c r="Z7" s="7">
+      <c r="Z7">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>40.168870000000005</v>
       </c>
-      <c r="AA7" s="7">
+      <c r="AA7">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>39.364419999999996</v>
       </c>
-      <c r="AB7" s="7">
+      <c r="AB7">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>351.43738999999999</v>
       </c>
@@ -14441,15 +14442,15 @@
       <c r="Y8">
         <v>1</v>
       </c>
-      <c r="Z8" s="7">
+      <c r="Z8">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AA8">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB8" s="7">
+      <c r="AB8">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -14538,15 +14539,15 @@
       <c r="Y9">
         <v>2</v>
       </c>
-      <c r="Z9" s="7">
+      <c r="Z9">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="7">
+      <c r="AA9">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB9" s="7">
+      <c r="AB9">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -14635,15 +14636,15 @@
       <c r="Y10">
         <v>2</v>
       </c>
-      <c r="Z10" s="7">
+      <c r="Z10">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.40335</v>
       </c>
-      <c r="AA10" s="7">
+      <c r="AA10">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>13.630700000000001</v>
       </c>
-      <c r="AB10" s="7">
+      <c r="AB10">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>252.08000999999999</v>
       </c>
@@ -14732,15 +14733,15 @@
       <c r="Y11">
         <v>2</v>
       </c>
-      <c r="Z11" s="7">
+      <c r="Z11">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>45.549299999999995</v>
       </c>
-      <c r="AA11" s="7">
+      <c r="AA11">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.7255</v>
       </c>
-      <c r="AB11" s="7">
+      <c r="AB11">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>300.69689999999997</v>
       </c>
@@ -14829,15 +14830,15 @@
       <c r="Y12">
         <v>2</v>
       </c>
-      <c r="Z12" s="7">
+      <c r="Z12">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.160129999999995</v>
       </c>
-      <c r="AA12" s="7">
+      <c r="AA12">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.085719999999998</v>
       </c>
-      <c r="AB12" s="7">
+      <c r="AB12">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>294.24756000000002</v>
       </c>
@@ -14926,15 +14927,15 @@
       <c r="Y13">
         <v>2</v>
       </c>
-      <c r="Z13" s="7">
+      <c r="Z13">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.520000000000003</v>
       </c>
-      <c r="AA13" s="7">
+      <c r="AA13">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.595600000000001</v>
       </c>
-      <c r="AB13" s="7">
+      <c r="AB13">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>294.37200000000001</v>
       </c>
@@ -15023,15 +15024,15 @@
       <c r="Y14">
         <v>2</v>
       </c>
-      <c r="Z14" s="7">
+      <c r="Z14">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.127039999999994</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AA14">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.248159999999999</v>
       </c>
-      <c r="AB14" s="7">
+      <c r="AB14">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>248.65590000000003</v>
       </c>
@@ -15120,15 +15121,15 @@
       <c r="Y15">
         <v>2</v>
       </c>
-      <c r="Z15" s="7">
+      <c r="Z15">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="7">
+      <c r="AA15">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="7">
+      <c r="AB15">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -15217,15 +15218,15 @@
       <c r="Y16">
         <v>3</v>
       </c>
-      <c r="Z16" s="7">
+      <c r="Z16">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="7">
+      <c r="AA16">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="7">
+      <c r="AB16">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -15314,15 +15315,15 @@
       <c r="Y17">
         <v>3</v>
       </c>
-      <c r="Z17" s="7">
+      <c r="Z17">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.216000000000001</v>
       </c>
-      <c r="AA17" s="7">
+      <c r="AA17">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.398399999999999</v>
       </c>
-      <c r="AB17" s="7">
+      <c r="AB17">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>269.70840000000004</v>
       </c>
@@ -15411,15 +15412,15 @@
       <c r="Y18">
         <v>3</v>
       </c>
-      <c r="Z18" s="7">
+      <c r="Z18">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>38.408099999999997</v>
       </c>
-      <c r="AA18" s="7">
+      <c r="AA18">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.256900000000002</v>
       </c>
-      <c r="AB18" s="7">
+      <c r="AB18">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.22229999999996</v>
       </c>
@@ -15508,15 +15509,15 @@
       <c r="Y19">
         <v>3</v>
       </c>
-      <c r="Z19" s="7">
+      <c r="Z19">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>19.262480000000004</v>
       </c>
-      <c r="AA19" s="7">
+      <c r="AA19">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.435779999999998</v>
       </c>
-      <c r="AB19" s="7">
+      <c r="AB19">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>278.64326</v>
       </c>
@@ -15605,15 +15606,15 @@
       <c r="Y20">
         <v>3</v>
       </c>
-      <c r="Z20" s="7">
+      <c r="Z20">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>46.895620000000001</v>
       </c>
-      <c r="AA20" s="7">
+      <c r="AA20">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>28.378319999999999</v>
       </c>
-      <c r="AB20" s="7">
+      <c r="AB20">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>295.65211999999997</v>
       </c>
@@ -15702,15 +15703,15 @@
       <c r="Y21">
         <v>3</v>
       </c>
-      <c r="Z21" s="7">
+      <c r="Z21">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.488300000000002</v>
       </c>
-      <c r="AA21" s="7">
+      <c r="AA21">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>20.916930000000001</v>
       </c>
-      <c r="AB21" s="7">
+      <c r="AB21">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>287.86532999999997</v>
       </c>
@@ -15799,15 +15800,15 @@
       <c r="Y22">
         <v>3</v>
       </c>
-      <c r="Z22" s="7">
+      <c r="Z22">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA22" s="7">
+      <c r="AA22">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB22" s="7">
+      <c r="AB22">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -15896,15 +15897,15 @@
       <c r="Y23">
         <v>4</v>
       </c>
-      <c r="Z23" s="7">
+      <c r="Z23">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA23" s="7">
+      <c r="AA23">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB23" s="7">
+      <c r="AB23">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -15993,15 +15994,15 @@
       <c r="Y24">
         <v>4</v>
       </c>
-      <c r="Z24" s="7">
+      <c r="Z24">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.418140000000001</v>
       </c>
-      <c r="AA24" s="7">
+      <c r="AA24">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.806249999999999</v>
       </c>
-      <c r="AB24" s="7">
+      <c r="AB24">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>302.70996000000002</v>
       </c>
@@ -16090,15 +16091,15 @@
       <c r="Y25">
         <v>4</v>
       </c>
-      <c r="Z25" s="7">
+      <c r="Z25">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.42615</v>
       </c>
-      <c r="AA25" s="7">
+      <c r="AA25">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.648400000000002</v>
       </c>
-      <c r="AB25" s="7">
+      <c r="AB25">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>290.70299999999997</v>
       </c>
@@ -16187,15 +16188,15 @@
       <c r="Y26">
         <v>4</v>
       </c>
-      <c r="Z26" s="7">
+      <c r="Z26">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.8264</v>
       </c>
-      <c r="AA26" s="7">
+      <c r="AA26">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.776960000000003</v>
       </c>
-      <c r="AB26" s="7">
+      <c r="AB26">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>284.83555999999999</v>
       </c>
@@ -16284,15 +16285,15 @@
       <c r="Y27">
         <v>4</v>
       </c>
-      <c r="Z27" s="7">
+      <c r="Z27">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.884300000000003</v>
       </c>
-      <c r="AA27" s="7">
+      <c r="AA27">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.052400000000002</v>
       </c>
-      <c r="AB27" s="7">
+      <c r="AB27">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>275.71320000000003</v>
       </c>
@@ -16381,15 +16382,15 @@
       <c r="Y28">
         <v>4</v>
       </c>
-      <c r="Z28" s="7">
+      <c r="Z28">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.825599999999998</v>
       </c>
-      <c r="AA28" s="7">
+      <c r="AA28">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.019359999999999</v>
       </c>
-      <c r="AB28" s="7">
+      <c r="AB28">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>269.02296000000001</v>
       </c>
@@ -16478,15 +16479,15 @@
       <c r="Y29">
         <v>4</v>
       </c>
-      <c r="Z29" s="7">
+      <c r="Z29">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA29" s="7">
+      <c r="AA29">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB29" s="7">
+      <c r="AB29">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -16575,15 +16576,15 @@
       <c r="Y30">
         <v>5</v>
       </c>
-      <c r="Z30" s="7">
+      <c r="Z30">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA30" s="7">
+      <c r="AA30">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB30" s="7">
+      <c r="AB30">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -16672,15 +16673,15 @@
       <c r="Y31">
         <v>5</v>
       </c>
-      <c r="Z31" s="7">
+      <c r="Z31">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.826280000000001</v>
       </c>
-      <c r="AA31" s="7">
+      <c r="AA31">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.759919999999997</v>
       </c>
-      <c r="AB31" s="7">
+      <c r="AB31">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>275.37732</v>
       </c>
@@ -16769,15 +16770,15 @@
       <c r="Y32">
         <v>5</v>
       </c>
-      <c r="Z32" s="7">
+      <c r="Z32">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.956</v>
       </c>
-      <c r="AA32" s="7">
+      <c r="AA32">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>17.643999999999998</v>
       </c>
-      <c r="AB32" s="7">
+      <c r="AB32">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>262.15199999999999</v>
       </c>
@@ -16866,15 +16867,15 @@
       <c r="Y33">
         <v>5</v>
       </c>
-      <c r="Z33" s="7">
+      <c r="Z33">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.531040000000004</v>
       </c>
-      <c r="AA33" s="7">
+      <c r="AA33">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.265520000000002</v>
       </c>
-      <c r="AB33" s="7">
+      <c r="AB33">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>271.44463999999999</v>
       </c>
@@ -16963,15 +16964,15 @@
       <c r="Y34">
         <v>5</v>
       </c>
-      <c r="Z34" s="7">
+      <c r="Z34">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.541799999999995</v>
       </c>
-      <c r="AA34" s="7">
+      <c r="AA34">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.959079999999997</v>
       </c>
-      <c r="AB34" s="7">
+      <c r="AB34">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>293.72631999999993</v>
       </c>
@@ -17060,15 +17061,15 @@
       <c r="Y35">
         <v>5</v>
       </c>
-      <c r="Z35" s="7">
+      <c r="Z35">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>48.21219</v>
       </c>
-      <c r="AA35" s="7">
+      <c r="AA35">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.617709999999999</v>
       </c>
-      <c r="AB35" s="7">
+      <c r="AB35">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>385.45676000000003</v>
       </c>
@@ -17157,15 +17158,15 @@
       <c r="Y36">
         <v>5</v>
       </c>
-      <c r="Z36" s="7">
+      <c r="Z36">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA36" s="7">
+      <c r="AA36">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB36" s="7">
+      <c r="AB36">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -17254,15 +17255,15 @@
       <c r="Y37">
         <v>6</v>
       </c>
-      <c r="Z37" s="7">
+      <c r="Z37">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA37" s="7">
+      <c r="AA37">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB37" s="7">
+      <c r="AB37">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -17351,15 +17352,15 @@
       <c r="Y38">
         <v>6</v>
       </c>
-      <c r="Z38" s="7">
+      <c r="Z38">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.410609999999998</v>
       </c>
-      <c r="AA38" s="7">
+      <c r="AA38">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.195460000000001</v>
       </c>
-      <c r="AB38" s="7">
+      <c r="AB38">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.04333999999994</v>
       </c>
@@ -17448,15 +17449,15 @@
       <c r="Y39">
         <v>6</v>
       </c>
-      <c r="Z39" s="7">
+      <c r="Z39">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.722919999999995</v>
       </c>
-      <c r="AA39" s="7">
+      <c r="AA39">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.601240000000001</v>
       </c>
-      <c r="AB39" s="7">
+      <c r="AB39">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>285.34032000000002</v>
       </c>
@@ -17545,15 +17546,15 @@
       <c r="Y40">
         <v>6</v>
       </c>
-      <c r="Z40" s="7">
+      <c r="Z40">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.099510000000002</v>
       </c>
-      <c r="AA40" s="7">
+      <c r="AA40">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.021539999999998</v>
       </c>
-      <c r="AB40" s="7">
+      <c r="AB40">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>300.80413999999996</v>
       </c>
@@ -17642,15 +17643,15 @@
       <c r="Y41">
         <v>6</v>
       </c>
-      <c r="Z41" s="7">
+      <c r="Z41">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.68216</v>
       </c>
-      <c r="AA41" s="7">
+      <c r="AA41">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.509119999999996</v>
       </c>
-      <c r="AB41" s="7">
+      <c r="AB41">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.93743999999998</v>
       </c>
@@ -17739,15 +17740,15 @@
       <c r="Y42">
         <v>6</v>
       </c>
-      <c r="Z42" s="7">
+      <c r="Z42">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.704960000000003</v>
       </c>
-      <c r="AA42" s="7">
+      <c r="AA42">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.790039999999998</v>
       </c>
-      <c r="AB42" s="7">
+      <c r="AB42">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>258.90940000000001</v>
       </c>
@@ -17836,15 +17837,15 @@
       <c r="Y43">
         <v>6</v>
       </c>
-      <c r="Z43" s="7">
+      <c r="Z43">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA43" s="7">
+      <c r="AA43">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB43" s="7">
+      <c r="AB43">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -17933,15 +17934,15 @@
       <c r="Y44">
         <v>7</v>
       </c>
-      <c r="Z44" s="7">
+      <c r="Z44">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA44" s="7">
+      <c r="AA44">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB44" s="7">
+      <c r="AB44">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -18030,15 +18031,15 @@
       <c r="Y45">
         <v>7</v>
       </c>
-      <c r="Z45" s="7">
+      <c r="Z45">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.652839999999998</v>
       </c>
-      <c r="AA45" s="7">
+      <c r="AA45">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>36.459060000000008</v>
       </c>
-      <c r="AB45" s="7">
+      <c r="AB45">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>303.45224999999999</v>
       </c>
@@ -18127,15 +18128,15 @@
       <c r="Y46">
         <v>7</v>
       </c>
-      <c r="Z46" s="7">
+      <c r="Z46">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>41.392199999999995</v>
       </c>
-      <c r="AA46" s="7">
+      <c r="AA46">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.843</v>
       </c>
-      <c r="AB46" s="7">
+      <c r="AB46">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>297.97020000000003</v>
       </c>
@@ -18224,15 +18225,15 @@
       <c r="Y47">
         <v>7</v>
       </c>
-      <c r="Z47" s="7">
+      <c r="Z47">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.755929999999999</v>
       </c>
-      <c r="AA47" s="7">
+      <c r="AA47">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>18.46893</v>
       </c>
-      <c r="AB47" s="7">
+      <c r="AB47">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>278.49552</v>
       </c>
@@ -18321,15 +18322,15 @@
       <c r="Y48">
         <v>7</v>
       </c>
-      <c r="Z48" s="7">
+      <c r="Z48">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.950479999999999</v>
       </c>
-      <c r="AA48" s="7">
+      <c r="AA48">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.82696</v>
       </c>
-      <c r="AB48" s="7">
+      <c r="AB48">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>285.17104</v>
       </c>
@@ -18418,15 +18419,15 @@
       <c r="Y49">
         <v>7</v>
       </c>
-      <c r="Z49" s="7">
+      <c r="Z49">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.034959999999998</v>
       </c>
-      <c r="AA49" s="7">
+      <c r="AA49">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.783439999999999</v>
       </c>
-      <c r="AB49" s="7">
+      <c r="AB49">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>276.31664000000001</v>
       </c>
@@ -18515,15 +18516,15 @@
       <c r="Y50">
         <v>7</v>
       </c>
-      <c r="Z50" s="7">
+      <c r="Z50">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA50" s="7">
+      <c r="AA50">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB50" s="7">
+      <c r="AB50">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -18612,15 +18613,15 @@
       <c r="Y51">
         <v>8</v>
       </c>
-      <c r="Z51" s="7">
+      <c r="Z51">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA51" s="7">
+      <c r="AA51">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB51" s="7">
+      <c r="AB51">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -18709,15 +18710,15 @@
       <c r="Y52">
         <v>8</v>
       </c>
-      <c r="Z52" s="7">
+      <c r="Z52">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.302399999999999</v>
       </c>
-      <c r="AA52" s="7">
+      <c r="AA52">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.08</v>
       </c>
-      <c r="AB52" s="7">
+      <c r="AB52">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>287.48159999999996</v>
       </c>
@@ -18806,15 +18807,15 @@
       <c r="Y53">
         <v>8</v>
       </c>
-      <c r="Z53" s="7">
+      <c r="Z53">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>50.979879999999994</v>
       </c>
-      <c r="AA53" s="7">
+      <c r="AA53">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.778080000000003</v>
       </c>
-      <c r="AB53" s="7">
+      <c r="AB53">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>320.75772000000001</v>
       </c>
@@ -18903,15 +18904,15 @@
       <c r="Y54">
         <v>8</v>
       </c>
-      <c r="Z54" s="7">
+      <c r="Z54">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.491260000000004</v>
       </c>
-      <c r="AA54" s="7">
+      <c r="AA54">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.680199999999996</v>
       </c>
-      <c r="AB54" s="7">
+      <c r="AB54">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>289.67303999999996</v>
       </c>
@@ -19000,15 +19001,15 @@
       <c r="Y55">
         <v>8</v>
       </c>
-      <c r="Z55" s="7">
+      <c r="Z55">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.22824</v>
       </c>
-      <c r="AA55" s="7">
+      <c r="AA55">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.052759999999999</v>
       </c>
-      <c r="AB55" s="7">
+      <c r="AB55">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>262.80912000000001</v>
       </c>
@@ -19097,15 +19098,15 @@
       <c r="Y56">
         <v>8</v>
       </c>
-      <c r="Z56" s="7">
+      <c r="Z56">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.959910000000001</v>
       </c>
-      <c r="AA56" s="7">
+      <c r="AA56">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.78511</v>
       </c>
-      <c r="AB56" s="7">
+      <c r="AB56">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>260.27933000000002</v>
       </c>
@@ -19194,15 +19195,15 @@
       <c r="Y57">
         <v>8</v>
       </c>
-      <c r="Z57" s="7">
+      <c r="Z57">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA57" s="7">
+      <c r="AA57">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB57" s="7">
+      <c r="AB57">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -19291,15 +19292,15 @@
       <c r="Y58">
         <v>9</v>
       </c>
-      <c r="Z58" s="7">
+      <c r="Z58">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA58" s="7">
+      <c r="AA58">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB58" s="7">
+      <c r="AB58">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -19388,15 +19389,15 @@
       <c r="Y59">
         <v>9</v>
       </c>
-      <c r="Z59" s="7">
+      <c r="Z59">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.039650000000002</v>
       </c>
-      <c r="AA59" s="7">
+      <c r="AA59">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.726200000000002</v>
       </c>
-      <c r="AB59" s="7">
+      <c r="AB59">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.09639999999996</v>
       </c>
@@ -19485,15 +19486,15 @@
       <c r="Y60">
         <v>9</v>
       </c>
-      <c r="Z60" s="7">
+      <c r="Z60">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.490799999999993</v>
       </c>
-      <c r="AA60" s="7">
+      <c r="AA60">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>17.897200000000002</v>
       </c>
-      <c r="AB60" s="7">
+      <c r="AB60">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>275.41310000000004</v>
       </c>
@@ -19582,15 +19583,15 @@
       <c r="Y61">
         <v>9</v>
       </c>
-      <c r="Z61" s="7">
+      <c r="Z61">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>38.143360000000001</v>
       </c>
-      <c r="AA61" s="7">
+      <c r="AA61">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>36.271840000000005</v>
       </c>
-      <c r="AB61" s="7">
+      <c r="AB61">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>297.74991999999997</v>
       </c>
@@ -19679,15 +19680,15 @@
       <c r="Y62">
         <v>9</v>
       </c>
-      <c r="Z62" s="7">
+      <c r="Z62">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.575199999999995</v>
       </c>
-      <c r="AA62" s="7">
+      <c r="AA62">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.965919999999997</v>
       </c>
-      <c r="AB62" s="7">
+      <c r="AB62">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>285.46512000000001</v>
       </c>
@@ -19776,15 +19777,15 @@
       <c r="Y63">
         <v>9</v>
       </c>
-      <c r="Z63" s="7">
+      <c r="Z63">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.72</v>
       </c>
-      <c r="AA63" s="7">
+      <c r="AA63">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>21.932500000000001</v>
       </c>
-      <c r="AB63" s="7">
+      <c r="AB63">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>250.71250000000001</v>
       </c>
@@ -19873,15 +19874,15 @@
       <c r="Y64">
         <v>9</v>
       </c>
-      <c r="Z64" s="7">
+      <c r="Z64">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA64" s="7">
+      <c r="AA64">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB64" s="7">
+      <c r="AB64">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -19970,15 +19971,15 @@
       <c r="Y65">
         <v>10</v>
       </c>
-      <c r="Z65" s="7">
+      <c r="Z65">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA65" s="7">
+      <c r="AA65">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB65" s="7">
+      <c r="AB65">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -20067,15 +20068,15 @@
       <c r="Y66">
         <v>10</v>
       </c>
-      <c r="Z66" s="7">
+      <c r="Z66">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>42.196599999999997</v>
       </c>
-      <c r="AA66" s="7">
+      <c r="AA66">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.577719999999999</v>
       </c>
-      <c r="AB66" s="7">
+      <c r="AB66">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>309.02276000000001</v>
       </c>
@@ -20164,15 +20165,15 @@
       <c r="Y67">
         <v>10</v>
       </c>
-      <c r="Z67" s="7">
+      <c r="Z67">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>30.749279999999999</v>
       </c>
-      <c r="AA67" s="7">
+      <c r="AA67">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>17.892899999999997</v>
       </c>
-      <c r="AB67" s="7">
+      <c r="AB67">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>269.85144000000003</v>
       </c>
@@ -20261,15 +20262,15 @@
       <c r="Y68">
         <v>10</v>
       </c>
-      <c r="Z68" s="7">
+      <c r="Z68">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.339269999999999</v>
       </c>
-      <c r="AA68" s="7">
+      <c r="AA68">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.16808</v>
       </c>
-      <c r="AB68" s="7">
+      <c r="AB68">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>285.53363999999999</v>
       </c>
@@ -20358,15 +20359,15 @@
       <c r="Y69">
         <v>10</v>
       </c>
-      <c r="Z69" s="7">
+      <c r="Z69">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.728300000000001</v>
       </c>
-      <c r="AA69" s="7">
+      <c r="AA69">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.663640000000001</v>
       </c>
-      <c r="AB69" s="7">
+      <c r="AB69">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.70398000000006</v>
       </c>
@@ -20455,15 +20456,15 @@
       <c r="Y70">
         <v>10</v>
       </c>
-      <c r="Z70" s="7">
+      <c r="Z70">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.663879999999999</v>
       </c>
-      <c r="AA70" s="7">
+      <c r="AA70">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>35.894860000000001</v>
       </c>
-      <c r="AB70" s="7">
+      <c r="AB70">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>290.69968000000006</v>
       </c>
@@ -20552,15 +20553,15 @@
       <c r="Y71">
         <v>10</v>
       </c>
-      <c r="Z71" s="7">
+      <c r="Z71">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA71" s="7">
+      <c r="AA71">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB71" s="7">
+      <c r="AB71">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -20649,15 +20650,15 @@
       <c r="Y72">
         <v>11</v>
       </c>
-      <c r="Z72" s="7">
+      <c r="Z72">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA72" s="7">
+      <c r="AA72">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB72" s="7">
+      <c r="AB72">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -20746,15 +20747,15 @@
       <c r="Y73">
         <v>11</v>
       </c>
-      <c r="Z73" s="7">
+      <c r="Z73">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.147419999999997</v>
       </c>
-      <c r="AA73" s="7">
+      <c r="AA73">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.673639999999999</v>
       </c>
-      <c r="AB73" s="7">
+      <c r="AB73">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>291.27252000000004</v>
       </c>
@@ -20843,15 +20844,15 @@
       <c r="Y74">
         <v>11</v>
       </c>
-      <c r="Z74" s="7">
+      <c r="Z74">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.79748</v>
       </c>
-      <c r="AA74" s="7">
+      <c r="AA74">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>14.869679999999999</v>
       </c>
-      <c r="AB74" s="7">
+      <c r="AB74">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>280.65408000000002</v>
       </c>
@@ -20940,15 +20941,15 @@
       <c r="Y75">
         <v>11</v>
       </c>
-      <c r="Z75" s="7">
+      <c r="Z75">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.093839999999993</v>
       </c>
-      <c r="AA75" s="7">
+      <c r="AA75">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.732599999999998</v>
       </c>
-      <c r="AB75" s="7">
+      <c r="AB75">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>297.92176000000001</v>
       </c>
@@ -21037,15 +21038,15 @@
       <c r="Y76">
         <v>11</v>
       </c>
-      <c r="Z76" s="7">
+      <c r="Z76">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.169889999999999</v>
       </c>
-      <c r="AA76" s="7">
+      <c r="AA76">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>11.17665</v>
       </c>
-      <c r="AB76" s="7">
+      <c r="AB76">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>259.60509000000002</v>
       </c>
@@ -21134,15 +21135,15 @@
       <c r="Y77">
         <v>11</v>
       </c>
-      <c r="Z77" s="7">
+      <c r="Z77">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.166559999999997</v>
       </c>
-      <c r="AA77" s="7">
+      <c r="AA77">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.529440000000001</v>
       </c>
-      <c r="AB77" s="7">
+      <c r="AB77">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>324.71647999999999</v>
       </c>
@@ -21231,15 +21232,15 @@
       <c r="Y78">
         <v>11</v>
       </c>
-      <c r="Z78" s="7">
+      <c r="Z78">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA78" s="7">
+      <c r="AA78">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB78" s="7">
+      <c r="AB78">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -21328,15 +21329,15 @@
       <c r="Y79">
         <v>12</v>
       </c>
-      <c r="Z79" s="7">
+      <c r="Z79">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA79" s="7">
+      <c r="AA79">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB79" s="7">
+      <c r="AB79">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -21425,15 +21426,15 @@
       <c r="Y80">
         <v>12</v>
       </c>
-      <c r="Z80" s="7">
+      <c r="Z80">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.226050000000004</v>
       </c>
-      <c r="AA80" s="7">
+      <c r="AA80">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.658390000000004</v>
       </c>
-      <c r="AB80" s="7">
+      <c r="AB80">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>280.45044999999999</v>
       </c>
@@ -21522,15 +21523,15 @@
       <c r="Y81">
         <v>12</v>
       </c>
-      <c r="Z81" s="7">
+      <c r="Z81">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.563700000000001</v>
       </c>
-      <c r="AA81" s="7">
+      <c r="AA81">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.05</v>
       </c>
-      <c r="AB81" s="7">
+      <c r="AB81">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>268.74539999999996</v>
       </c>
@@ -21619,15 +21620,15 @@
       <c r="Y82">
         <v>12</v>
       </c>
-      <c r="Z82" s="7">
+      <c r="Z82">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.45889</v>
       </c>
-      <c r="AA82" s="7">
+      <c r="AA82">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.923759999999998</v>
       </c>
-      <c r="AB82" s="7">
+      <c r="AB82">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>274.64092999999997</v>
       </c>
@@ -21716,15 +21717,15 @@
       <c r="Y83">
         <v>12</v>
       </c>
-      <c r="Z83" s="7">
+      <c r="Z83">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.111499999999999</v>
       </c>
-      <c r="AA83" s="7">
+      <c r="AA83">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>34.189</v>
       </c>
-      <c r="AB83" s="7">
+      <c r="AB83">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>301.43599999999998</v>
       </c>
@@ -21813,15 +21814,15 @@
       <c r="Y84">
         <v>12</v>
       </c>
-      <c r="Z84" s="7">
+      <c r="Z84">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.883199999999999</v>
       </c>
-      <c r="AA84" s="7">
+      <c r="AA84">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.041520000000002</v>
       </c>
-      <c r="AB84" s="7">
+      <c r="AB84">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>245.47476</v>
       </c>
@@ -21910,15 +21911,15 @@
       <c r="Y85">
         <v>12</v>
       </c>
-      <c r="Z85" s="7">
+      <c r="Z85">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA85" s="7">
+      <c r="AA85">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB85" s="7">
+      <c r="AB85">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -22007,15 +22008,15 @@
       <c r="Y86">
         <v>13</v>
       </c>
-      <c r="Z86" s="7">
+      <c r="Z86">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA86" s="7">
+      <c r="AA86">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB86" s="7">
+      <c r="AB86">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -22104,15 +22105,15 @@
       <c r="Y87">
         <v>13</v>
       </c>
-      <c r="Z87" s="7">
+      <c r="Z87">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.56803</v>
       </c>
-      <c r="AA87" s="7">
+      <c r="AA87">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.027909999999999</v>
       </c>
-      <c r="AB87" s="7">
+      <c r="AB87">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.57214999999997</v>
       </c>
@@ -22201,15 +22202,15 @@
       <c r="Y88">
         <v>13</v>
       </c>
-      <c r="Z88" s="7">
+      <c r="Z88">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.993840000000006</v>
       </c>
-      <c r="AA88" s="7">
+      <c r="AA88">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.049040000000002</v>
       </c>
-      <c r="AB88" s="7">
+      <c r="AB88">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>280.34888000000001</v>
       </c>
@@ -22298,15 +22299,15 @@
       <c r="Y89">
         <v>13</v>
       </c>
-      <c r="Z89" s="7">
+      <c r="Z89">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.334300000000006</v>
       </c>
-      <c r="AA89" s="7">
+      <c r="AA89">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.14284</v>
       </c>
-      <c r="AB89" s="7">
+      <c r="AB89">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>293.31301999999999</v>
       </c>
@@ -22395,15 +22396,15 @@
       <c r="Y90">
         <v>13</v>
       </c>
-      <c r="Z90" s="7">
+      <c r="Z90">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>43.368699999999997</v>
       </c>
-      <c r="AA90" s="7">
+      <c r="AA90">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>36.975169999999999</v>
       </c>
-      <c r="AB90" s="7">
+      <c r="AB90">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>309.70616999999999</v>
       </c>
@@ -22492,15 +22493,15 @@
       <c r="Y91">
         <v>13</v>
       </c>
-      <c r="Z91" s="7">
+      <c r="Z91">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.801000000000009</v>
       </c>
-      <c r="AA91" s="7">
+      <c r="AA91">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>18.356999999999999</v>
       </c>
-      <c r="AB91" s="7">
+      <c r="AB91">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>272.70150000000001</v>
       </c>
@@ -22589,15 +22590,15 @@
       <c r="Y92">
         <v>13</v>
       </c>
-      <c r="Z92" s="7">
+      <c r="Z92">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA92" s="7">
+      <c r="AA92">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB92" s="7">
+      <c r="AB92">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -22686,15 +22687,15 @@
       <c r="Y93">
         <v>14</v>
       </c>
-      <c r="Z93" s="7">
+      <c r="Z93">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA93" s="7">
+      <c r="AA93">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB93" s="7">
+      <c r="AB93">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -22783,15 +22784,15 @@
       <c r="Y94">
         <v>14</v>
       </c>
-      <c r="Z94" s="7">
+      <c r="Z94">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.321120000000001</v>
       </c>
-      <c r="AA94" s="7">
+      <c r="AA94">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.73104</v>
       </c>
-      <c r="AB94" s="7">
+      <c r="AB94">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>273.65665999999999</v>
       </c>
@@ -22880,15 +22881,15 @@
       <c r="Y95">
         <v>14</v>
       </c>
-      <c r="Z95" s="7">
+      <c r="Z95">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.240809999999996</v>
       </c>
-      <c r="AA95" s="7">
+      <c r="AA95">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.033559999999998</v>
       </c>
-      <c r="AB95" s="7">
+      <c r="AB95">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>278.40156000000002</v>
       </c>
@@ -22977,15 +22978,15 @@
       <c r="Y96">
         <v>14</v>
       </c>
-      <c r="Z96" s="7">
+      <c r="Z96">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.064</v>
       </c>
-      <c r="AA96" s="7">
+      <c r="AA96">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>20.591999999999999</v>
       </c>
-      <c r="AB96" s="7">
+      <c r="AB96">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>280.67599999999999</v>
       </c>
@@ -23074,15 +23075,15 @@
       <c r="Y97">
         <v>14</v>
       </c>
-      <c r="Z97" s="7">
+      <c r="Z97">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.496759999999998</v>
       </c>
-      <c r="AA97" s="7">
+      <c r="AA97">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.54402</v>
       </c>
-      <c r="AB97" s="7">
+      <c r="AB97">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>272.80655999999999</v>
       </c>
@@ -23171,15 +23172,15 @@
       <c r="Y98">
         <v>14</v>
       </c>
-      <c r="Z98" s="7">
+      <c r="Z98">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.090260000000001</v>
       </c>
-      <c r="AA98" s="7">
+      <c r="AA98">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>35.809650000000005</v>
       </c>
-      <c r="AB98" s="7">
+      <c r="AB98">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>322.19199000000003</v>
       </c>
@@ -23268,15 +23269,15 @@
       <c r="Y99">
         <v>14</v>
       </c>
-      <c r="Z99" s="7">
+      <c r="Z99">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA99" s="7">
+      <c r="AA99">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB99" s="7">
+      <c r="AB99">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -23365,15 +23366,15 @@
       <c r="Y100">
         <v>15</v>
       </c>
-      <c r="Z100" s="7">
+      <c r="Z100">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA100" s="7">
+      <c r="AA100">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB100" s="7">
+      <c r="AB100">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -23462,15 +23463,15 @@
       <c r="Y101">
         <v>15</v>
       </c>
-      <c r="Z101" s="7">
+      <c r="Z101">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>25.651149999999998</v>
       </c>
-      <c r="AA101" s="7">
+      <c r="AA101">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.531950000000002</v>
       </c>
-      <c r="AB101" s="7">
+      <c r="AB101">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>268.87349999999998</v>
       </c>
@@ -23559,15 +23560,15 @@
       <c r="Y102">
         <v>15</v>
       </c>
-      <c r="Z102" s="7">
+      <c r="Z102">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>38.887749999999997</v>
       </c>
-      <c r="AA102" s="7">
+      <c r="AA102">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>37.008249999999997</v>
       </c>
-      <c r="AB102" s="7">
+      <c r="AB102">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>301.57024999999999</v>
       </c>
@@ -23656,15 +23657,15 @@
       <c r="Y103">
         <v>15</v>
       </c>
-      <c r="Z103" s="7">
+      <c r="Z103">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>41.489139999999999</v>
       </c>
-      <c r="AA103" s="7">
+      <c r="AA103">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.770739999999996</v>
       </c>
-      <c r="AB103" s="7">
+      <c r="AB103">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>304.00061999999997</v>
       </c>
@@ -23753,15 +23754,15 @@
       <c r="Y104">
         <v>15</v>
       </c>
-      <c r="Z104" s="7">
+      <c r="Z104">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.859500000000001</v>
       </c>
-      <c r="AA104" s="7">
+      <c r="AA104">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.330500000000001</v>
       </c>
-      <c r="AB104" s="7">
+      <c r="AB104">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>288.76049999999998</v>
       </c>
@@ -23850,15 +23851,15 @@
       <c r="Y105">
         <v>15</v>
       </c>
-      <c r="Z105" s="7">
+      <c r="Z105">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.04064</v>
       </c>
-      <c r="AA105" s="7">
+      <c r="AA105">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.14311</v>
       </c>
-      <c r="AB105" s="7">
+      <c r="AB105">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>271.92766999999998</v>
       </c>
@@ -23947,15 +23948,15 @@
       <c r="Y106">
         <v>15</v>
       </c>
-      <c r="Z106" s="7">
+      <c r="Z106">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA106" s="7">
+      <c r="AA106">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB106" s="7">
+      <c r="AB106">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -24044,15 +24045,15 @@
       <c r="Y107">
         <v>16</v>
       </c>
-      <c r="Z107" s="7">
+      <c r="Z107">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA107" s="7">
+      <c r="AA107">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB107" s="7">
+      <c r="AB107">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -24141,15 +24142,15 @@
       <c r="Y108">
         <v>16</v>
       </c>
-      <c r="Z108" s="7">
+      <c r="Z108">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.26052</v>
       </c>
-      <c r="AA108" s="7">
+      <c r="AA108">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>35.433150000000005</v>
       </c>
-      <c r="AB108" s="7">
+      <c r="AB108">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>295.76652000000001</v>
       </c>
@@ -24238,15 +24239,15 @@
       <c r="Y109">
         <v>16</v>
       </c>
-      <c r="Z109" s="7">
+      <c r="Z109">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.703100000000003</v>
       </c>
-      <c r="AA109" s="7">
+      <c r="AA109">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.786059999999999</v>
       </c>
-      <c r="AB109" s="7">
+      <c r="AB109">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>281.33729999999997</v>
       </c>
@@ -24335,15 +24336,15 @@
       <c r="Y110">
         <v>16</v>
       </c>
-      <c r="Z110" s="7">
+      <c r="Z110">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.270140000000001</v>
       </c>
-      <c r="AA110" s="7">
+      <c r="AA110">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.561610000000002</v>
       </c>
-      <c r="AB110" s="7">
+      <c r="AB110">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>267.40190999999999</v>
       </c>
@@ -24432,15 +24433,15 @@
       <c r="Y111">
         <v>16</v>
       </c>
-      <c r="Z111" s="7">
+      <c r="Z111">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.964199999999998</v>
       </c>
-      <c r="AA111" s="7">
+      <c r="AA111">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.1496</v>
       </c>
-      <c r="AB111" s="7">
+      <c r="AB111">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.33199999999999</v>
       </c>
@@ -24529,15 +24530,15 @@
       <c r="Y112">
         <v>16</v>
       </c>
-      <c r="Z112" s="7">
+      <c r="Z112">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.779900000000001</v>
       </c>
-      <c r="AA112" s="7">
+      <c r="AA112">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>39.263300000000001</v>
       </c>
-      <c r="AB112" s="7">
+      <c r="AB112">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>320.48545000000001</v>
       </c>
@@ -24626,15 +24627,15 @@
       <c r="Y113">
         <v>16</v>
       </c>
-      <c r="Z113" s="7">
+      <c r="Z113">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA113" s="7">
+      <c r="AA113">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB113" s="7">
+      <c r="AB113">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -24723,15 +24724,15 @@
       <c r="Y114">
         <v>17</v>
       </c>
-      <c r="Z114" s="7">
+      <c r="Z114">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA114" s="7">
+      <c r="AA114">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB114" s="7">
+      <c r="AB114">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -24820,15 +24821,15 @@
       <c r="Y115">
         <v>17</v>
       </c>
-      <c r="Z115" s="7">
+      <c r="Z115">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.237569999999998</v>
       </c>
-      <c r="AA115" s="7">
+      <c r="AA115">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.175109999999997</v>
       </c>
-      <c r="AB115" s="7">
+      <c r="AB115">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>277.73508000000004</v>
       </c>
@@ -24917,15 +24918,15 @@
       <c r="Y116">
         <v>17</v>
       </c>
-      <c r="Z116" s="7">
+      <c r="Z116">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.580850000000002</v>
       </c>
-      <c r="AA116" s="7">
+      <c r="AA116">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.648150000000001</v>
       </c>
-      <c r="AB116" s="7">
+      <c r="AB116">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>278.25700000000001</v>
       </c>
@@ -25014,15 +25015,15 @@
       <c r="Y117">
         <v>17</v>
       </c>
-      <c r="Z117" s="7">
+      <c r="Z117">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>43.222659999999998</v>
       </c>
-      <c r="AA117" s="7">
+      <c r="AA117">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>39.807979999999993</v>
       </c>
-      <c r="AB117" s="7">
+      <c r="AB117">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>307.14148</v>
       </c>
@@ -25111,15 +25112,15 @@
       <c r="Y118">
         <v>17</v>
       </c>
-      <c r="Z118" s="7">
+      <c r="Z118">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>38.64443</v>
       </c>
-      <c r="AA118" s="7">
+      <c r="AA118">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>32.685449999999996</v>
       </c>
-      <c r="AB118" s="7">
+      <c r="AB118">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>296.65936999999997</v>
       </c>
@@ -25208,15 +25209,15 @@
       <c r="Y119">
         <v>17</v>
       </c>
-      <c r="Z119" s="7">
+      <c r="Z119">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>46.489920000000005</v>
       </c>
-      <c r="AA119" s="7">
+      <c r="AA119">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.208639999999999</v>
       </c>
-      <c r="AB119" s="7">
+      <c r="AB119">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>331.26519999999999</v>
       </c>
@@ -25305,15 +25306,15 @@
       <c r="Y120">
         <v>17</v>
       </c>
-      <c r="Z120" s="7">
+      <c r="Z120">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA120" s="7">
+      <c r="AA120">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB120" s="7">
+      <c r="AB120">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -25402,15 +25403,15 @@
       <c r="Y121">
         <v>18</v>
       </c>
-      <c r="Z121" s="7">
+      <c r="Z121">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA121" s="7">
+      <c r="AA121">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB121" s="7">
+      <c r="AB121">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -25499,15 +25500,15 @@
       <c r="Y122">
         <v>18</v>
       </c>
-      <c r="Z122" s="7">
+      <c r="Z122">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>45.841440000000006</v>
       </c>
-      <c r="AA122" s="7">
+      <c r="AA122">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.095099999999999</v>
       </c>
-      <c r="AB122" s="7">
+      <c r="AB122">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>301.47854000000001</v>
       </c>
@@ -25596,15 +25597,15 @@
       <c r="Y123">
         <v>18</v>
       </c>
-      <c r="Z123" s="7">
+      <c r="Z123">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.068670000000001</v>
       </c>
-      <c r="AA123" s="7">
+      <c r="AA123">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>34.018059999999998</v>
       </c>
-      <c r="AB123" s="7">
+      <c r="AB123">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>284.97897</v>
       </c>
@@ -25693,15 +25694,15 @@
       <c r="Y124">
         <v>18</v>
       </c>
-      <c r="Z124" s="7">
+      <c r="Z124">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>19.183499999999999</v>
       </c>
-      <c r="AA124" s="7">
+      <c r="AA124">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>21.035699999999999</v>
       </c>
-      <c r="AB124" s="7">
+      <c r="AB124">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>259.44029999999998</v>
       </c>
@@ -25790,15 +25791,15 @@
       <c r="Y125">
         <v>18</v>
       </c>
-      <c r="Z125" s="7">
+      <c r="Z125">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>30.495930000000001</v>
       </c>
-      <c r="AA125" s="7">
+      <c r="AA125">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>28.453990000000001</v>
       </c>
-      <c r="AB125" s="7">
+      <c r="AB125">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>288.71256000000005</v>
       </c>
@@ -25887,15 +25888,15 @@
       <c r="Y126">
         <v>18</v>
       </c>
-      <c r="Z126" s="7">
+      <c r="Z126">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.379140000000003</v>
       </c>
-      <c r="AA126" s="7">
+      <c r="AA126">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>15.660440000000001</v>
       </c>
-      <c r="AB126" s="7">
+      <c r="AB126">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>260.02488999999997</v>
       </c>
@@ -25984,15 +25985,15 @@
       <c r="Y127">
         <v>18</v>
       </c>
-      <c r="Z127" s="7">
+      <c r="Z127">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA127" s="7">
+      <c r="AA127">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB127" s="7">
+      <c r="AB127">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -26081,15 +26082,15 @@
       <c r="Y128">
         <v>19</v>
       </c>
-      <c r="Z128" s="7">
+      <c r="Z128">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA128" s="7">
+      <c r="AA128">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB128" s="7">
+      <c r="AB128">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -26178,15 +26179,15 @@
       <c r="Y129">
         <v>19</v>
       </c>
-      <c r="Z129" s="7">
+      <c r="Z129">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.079419999999999</v>
       </c>
-      <c r="AA129" s="7">
+      <c r="AA129">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>36.576540000000001</v>
       </c>
-      <c r="AB129" s="7">
+      <c r="AB129">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>307.39477999999997</v>
       </c>
@@ -26275,15 +26276,15 @@
       <c r="Y130">
         <v>19</v>
       </c>
-      <c r="Z130" s="7">
+      <c r="Z130">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.05312</v>
       </c>
-      <c r="AA130" s="7">
+      <c r="AA130">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.766079999999999</v>
       </c>
-      <c r="AB130" s="7">
+      <c r="AB130">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>288.61511999999999</v>
       </c>
@@ -26372,15 +26373,15 @@
       <c r="Y131">
         <v>19</v>
       </c>
-      <c r="Z131" s="7">
+      <c r="Z131">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.114780000000003</v>
       </c>
-      <c r="AA131" s="7">
+      <c r="AA131">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.113400000000002</v>
       </c>
-      <c r="AB131" s="7">
+      <c r="AB131">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>282.37880000000001</v>
       </c>
@@ -26469,15 +26470,15 @@
       <c r="Y132">
         <v>19</v>
       </c>
-      <c r="Z132" s="7">
+      <c r="Z132">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.549080000000004</v>
       </c>
-      <c r="AA132" s="7">
+      <c r="AA132">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.219900000000003</v>
       </c>
-      <c r="AB132" s="7">
+      <c r="AB132">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>285.74256000000003</v>
       </c>
@@ -26566,15 +26567,15 @@
       <c r="Y133">
         <v>19</v>
       </c>
-      <c r="Z133" s="7">
+      <c r="Z133">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.477760000000004</v>
       </c>
-      <c r="AA133" s="7">
+      <c r="AA133">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>17.930449999999997</v>
       </c>
-      <c r="AB133" s="7">
+      <c r="AB133">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>227.66125999999997</v>
       </c>
@@ -26663,15 +26664,15 @@
       <c r="Y134">
         <v>19</v>
       </c>
-      <c r="Z134" s="7">
+      <c r="Z134">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA134" s="7">
+      <c r="AA134">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB134" s="7">
+      <c r="AB134">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -26760,15 +26761,15 @@
       <c r="Y135">
         <v>20</v>
       </c>
-      <c r="Z135" s="7">
+      <c r="Z135">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA135" s="7">
+      <c r="AA135">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB135" s="7">
+      <c r="AB135">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -26857,15 +26858,15 @@
       <c r="Y136">
         <v>20</v>
       </c>
-      <c r="Z136" s="7">
+      <c r="Z136">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.414919999999999</v>
       </c>
-      <c r="AA136" s="7">
+      <c r="AA136">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.343</v>
       </c>
-      <c r="AB136" s="7">
+      <c r="AB136">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>281.36081999999999</v>
       </c>
@@ -26954,15 +26955,15 @@
       <c r="Y137">
         <v>20</v>
       </c>
-      <c r="Z137" s="7">
+      <c r="Z137">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.535139999999998</v>
       </c>
-      <c r="AA137" s="7">
+      <c r="AA137">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.825700000000001</v>
       </c>
-      <c r="AB137" s="7">
+      <c r="AB137">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>280.22879999999998</v>
       </c>
@@ -27051,15 +27052,15 @@
       <c r="Y138">
         <v>20</v>
       </c>
-      <c r="Z138" s="7">
+      <c r="Z138">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.454720000000002</v>
       </c>
-      <c r="AA138" s="7">
+      <c r="AA138">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.299480000000003</v>
       </c>
-      <c r="AB138" s="7">
+      <c r="AB138">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>277.68619999999999</v>
       </c>
@@ -27148,15 +27149,15 @@
       <c r="Y139">
         <v>20</v>
       </c>
-      <c r="Z139" s="7">
+      <c r="Z139">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>47.710599999999999</v>
       </c>
-      <c r="AA139" s="7">
+      <c r="AA139">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>38.708599999999997</v>
       </c>
-      <c r="AB139" s="7">
+      <c r="AB139">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>310.56900000000002</v>
       </c>
@@ -27245,15 +27246,15 @@
       <c r="Y140">
         <v>20</v>
       </c>
-      <c r="Z140" s="7">
+      <c r="Z140">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.942320000000002</v>
       </c>
-      <c r="AA140" s="7">
+      <c r="AA140">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>18.0258</v>
       </c>
-      <c r="AB140" s="7">
+      <c r="AB140">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>283.32859999999999</v>
       </c>
@@ -27342,15 +27343,15 @@
       <c r="Y141">
         <v>20</v>
       </c>
-      <c r="Z141" s="7">
+      <c r="Z141">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA141" s="7">
+      <c r="AA141">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB141" s="7">
+      <c r="AB141">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -27439,15 +27440,15 @@
       <c r="Y142">
         <v>21</v>
       </c>
-      <c r="Z142" s="7">
+      <c r="Z142">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA142" s="7">
+      <c r="AA142">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB142" s="7">
+      <c r="AB142">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -27536,15 +27537,15 @@
       <c r="Y143">
         <v>21</v>
       </c>
-      <c r="Z143" s="7">
+      <c r="Z143">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.584389999999999</v>
       </c>
-      <c r="AA143" s="7">
+      <c r="AA143">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.618169999999999</v>
       </c>
-      <c r="AB143" s="7">
+      <c r="AB143">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>277.41428000000002</v>
       </c>
@@ -27633,15 +27634,15 @@
       <c r="Y144">
         <v>21</v>
       </c>
-      <c r="Z144" s="7">
+      <c r="Z144">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.711149999999996</v>
       </c>
-      <c r="AA144" s="7">
+      <c r="AA144">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.02468</v>
       </c>
-      <c r="AB144" s="7">
+      <c r="AB144">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>288.67122000000001</v>
       </c>
@@ -27730,15 +27731,15 @@
       <c r="Y145">
         <v>21</v>
       </c>
-      <c r="Z145" s="7">
+      <c r="Z145">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.479529999999997</v>
       </c>
-      <c r="AA145" s="7">
+      <c r="AA145">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.022860000000001</v>
       </c>
-      <c r="AB145" s="7">
+      <c r="AB145">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>298.41750000000002</v>
       </c>
@@ -27827,15 +27828,15 @@
       <c r="Y146">
         <v>21</v>
       </c>
-      <c r="Z146" s="7">
+      <c r="Z146">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.66</v>
       </c>
-      <c r="AA146" s="7">
+      <c r="AA146">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>36.174599999999998</v>
       </c>
-      <c r="AB146" s="7">
+      <c r="AB146">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>310.02972000000005</v>
       </c>
@@ -27924,15 +27925,15 @@
       <c r="Y147">
         <v>21</v>
       </c>
-      <c r="Z147" s="7">
+      <c r="Z147">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>25.197589999999998</v>
       </c>
-      <c r="AA147" s="7">
+      <c r="AA147">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>21.092610000000001</v>
       </c>
-      <c r="AB147" s="7">
+      <c r="AB147">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>264.11615999999998</v>
       </c>
@@ -28021,15 +28022,15 @@
       <c r="Y148">
         <v>21</v>
       </c>
-      <c r="Z148" s="7">
+      <c r="Z148">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA148" s="7">
+      <c r="AA148">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB148" s="7">
+      <c r="AB148">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -28118,15 +28119,15 @@
       <c r="Y149">
         <v>22</v>
       </c>
-      <c r="Z149" s="7">
+      <c r="Z149">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA149" s="7">
+      <c r="AA149">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB149" s="7">
+      <c r="AB149">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -28215,15 +28216,15 @@
       <c r="Y150">
         <v>22</v>
       </c>
-      <c r="Z150" s="7">
+      <c r="Z150">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.576430000000002</v>
       </c>
-      <c r="AA150" s="7">
+      <c r="AA150">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>38.275379999999998</v>
       </c>
-      <c r="AB150" s="7">
+      <c r="AB150">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>295.98734999999999</v>
       </c>
@@ -28312,15 +28313,15 @@
       <c r="Y151">
         <v>22</v>
       </c>
-      <c r="Z151" s="7">
+      <c r="Z151">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>43.392960000000002</v>
       </c>
-      <c r="AA151" s="7">
+      <c r="AA151">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.898299999999999</v>
       </c>
-      <c r="AB151" s="7">
+      <c r="AB151">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>301.92786000000001</v>
       </c>
@@ -28409,15 +28410,15 @@
       <c r="Y152">
         <v>22</v>
       </c>
-      <c r="Z152" s="7">
+      <c r="Z152">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.743040000000001</v>
       </c>
-      <c r="AA152" s="7">
+      <c r="AA152">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.005160000000004</v>
       </c>
-      <c r="AB152" s="7">
+      <c r="AB152">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>281.80047999999999</v>
       </c>
@@ -28506,15 +28507,15 @@
       <c r="Y153">
         <v>22</v>
       </c>
-      <c r="Z153" s="7">
+      <c r="Z153">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>20.11797</v>
       </c>
-      <c r="AA153" s="7">
+      <c r="AA153">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>13.718789999999998</v>
       </c>
-      <c r="AB153" s="7">
+      <c r="AB153">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>257.06295</v>
       </c>
@@ -28603,15 +28604,15 @@
       <c r="Y154">
         <v>22</v>
       </c>
-      <c r="Z154" s="7">
+      <c r="Z154">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>18.997449999999997</v>
       </c>
-      <c r="AA154" s="7">
+      <c r="AA154">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>2.38937</v>
       </c>
-      <c r="AB154" s="7">
+      <c r="AB154">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>223.15149</v>
       </c>
@@ -28700,15 +28701,15 @@
       <c r="Y155">
         <v>22</v>
       </c>
-      <c r="Z155" s="7">
+      <c r="Z155">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA155" s="7">
+      <c r="AA155">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB155" s="7">
+      <c r="AB155">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -28797,15 +28798,15 @@
       <c r="Y156">
         <v>23</v>
       </c>
-      <c r="Z156" s="7">
+      <c r="Z156">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA156" s="7">
+      <c r="AA156">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB156" s="7">
+      <c r="AB156">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -28894,15 +28895,15 @@
       <c r="Y157">
         <v>23</v>
       </c>
-      <c r="Z157" s="7">
+      <c r="Z157">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>46.06147</v>
       </c>
-      <c r="AA157" s="7">
+      <c r="AA157">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.473990000000001</v>
       </c>
-      <c r="AB157" s="7">
+      <c r="AB157">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>298.84217999999998</v>
       </c>
@@ -28991,15 +28992,15 @@
       <c r="Y158">
         <v>23</v>
       </c>
-      <c r="Z158" s="7">
+      <c r="Z158">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.810559999999995</v>
       </c>
-      <c r="AA158" s="7">
+      <c r="AA158">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>20.520160000000001</v>
       </c>
-      <c r="AB158" s="7">
+      <c r="AB158">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>280.67856</v>
       </c>
@@ -29088,15 +29089,15 @@
       <c r="Y159">
         <v>23</v>
       </c>
-      <c r="Z159" s="7">
+      <c r="Z159">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.213070000000002</v>
       </c>
-      <c r="AA159" s="7">
+      <c r="AA159">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>32.31212</v>
       </c>
-      <c r="AB159" s="7">
+      <c r="AB159">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>294.82578000000001</v>
       </c>
@@ -29185,15 +29186,15 @@
       <c r="Y160">
         <v>23</v>
       </c>
-      <c r="Z160" s="7">
+      <c r="Z160">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>38.381799999999998</v>
       </c>
-      <c r="AA160" s="7">
+      <c r="AA160">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.188020000000002</v>
       </c>
-      <c r="AB160" s="7">
+      <c r="AB160">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>291.43389999999994</v>
       </c>
@@ -29282,15 +29283,15 @@
       <c r="Y161">
         <v>23</v>
       </c>
-      <c r="Z161" s="7">
+      <c r="Z161">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.685600000000001</v>
       </c>
-      <c r="AA161" s="7">
+      <c r="AA161">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>20.936160000000005</v>
       </c>
-      <c r="AB161" s="7">
+      <c r="AB161">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>281.63376</v>
       </c>
@@ -29379,15 +29380,15 @@
       <c r="Y162">
         <v>23</v>
       </c>
-      <c r="Z162" s="7">
+      <c r="Z162">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA162" s="7">
+      <c r="AA162">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB162" s="7">
+      <c r="AB162">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -29476,15 +29477,15 @@
       <c r="Y163">
         <v>24</v>
       </c>
-      <c r="Z163" s="7">
+      <c r="Z163">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA163" s="7">
+      <c r="AA163">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB163" s="7">
+      <c r="AB163">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -29573,15 +29574,15 @@
       <c r="Y164">
         <v>24</v>
       </c>
-      <c r="Z164" s="7">
+      <c r="Z164">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.634360000000001</v>
       </c>
-      <c r="AA164" s="7">
+      <c r="AA164">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.12706</v>
       </c>
-      <c r="AB164" s="7">
+      <c r="AB164">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>283.27332000000001</v>
       </c>
@@ -29670,15 +29671,15 @@
       <c r="Y165">
         <v>24</v>
       </c>
-      <c r="Z165" s="7">
+      <c r="Z165">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.82995</v>
       </c>
-      <c r="AA165" s="7">
+      <c r="AA165">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>21.67765</v>
       </c>
-      <c r="AB165" s="7">
+      <c r="AB165">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>277.92424999999997</v>
       </c>
@@ -29767,15 +29768,15 @@
       <c r="Y166">
         <v>24</v>
       </c>
-      <c r="Z166" s="7">
+      <c r="Z166">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>43.283160000000002</v>
       </c>
-      <c r="AA166" s="7">
+      <c r="AA166">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.851590000000002</v>
       </c>
-      <c r="AB166" s="7">
+      <c r="AB166">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>296.03543999999999</v>
       </c>
@@ -29864,15 +29865,15 @@
       <c r="Y167">
         <v>24</v>
       </c>
-      <c r="Z167" s="7">
+      <c r="Z167">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.629540000000002</v>
       </c>
-      <c r="AA167" s="7">
+      <c r="AA167">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>20.179479999999998</v>
       </c>
-      <c r="AB167" s="7">
+      <c r="AB167">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>263.74315999999999</v>
       </c>
@@ -29961,15 +29962,15 @@
       <c r="Y168">
         <v>24</v>
       </c>
-      <c r="Z168" s="7">
+      <c r="Z168">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.281819999999996</v>
       </c>
-      <c r="AA168" s="7">
+      <c r="AA168">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.808520000000001</v>
       </c>
-      <c r="AB168" s="7">
+      <c r="AB168">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>253.49264999999997</v>
       </c>
@@ -30058,15 +30059,15 @@
       <c r="Y169">
         <v>24</v>
       </c>
-      <c r="Z169" s="7">
+      <c r="Z169">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA169" s="7">
+      <c r="AA169">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB169" s="7">
+      <c r="AB169">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -30155,15 +30156,15 @@
       <c r="Y170">
         <v>25</v>
       </c>
-      <c r="Z170" s="7">
+      <c r="Z170">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA170" s="7">
+      <c r="AA170">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB170" s="7">
+      <c r="AB170">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -30252,15 +30253,15 @@
       <c r="Y171">
         <v>25</v>
       </c>
-      <c r="Z171" s="7">
+      <c r="Z171">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.130280000000003</v>
       </c>
-      <c r="AA171" s="7">
+      <c r="AA171">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>17.55931</v>
       </c>
-      <c r="AB171" s="7">
+      <c r="AB171">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>272.19141999999999</v>
       </c>
@@ -30349,15 +30350,15 @@
       <c r="Y172">
         <v>25</v>
       </c>
-      <c r="Z172" s="7">
+      <c r="Z172">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.898650000000004</v>
       </c>
-      <c r="AA172" s="7">
+      <c r="AA172">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.394490000000001</v>
       </c>
-      <c r="AB172" s="7">
+      <c r="AB172">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>276.71777999999995</v>
       </c>
@@ -30446,15 +30447,15 @@
       <c r="Y173">
         <v>25</v>
       </c>
-      <c r="Z173" s="7">
+      <c r="Z173">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>48.266649999999998</v>
       </c>
-      <c r="AA173" s="7">
+      <c r="AA173">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.469000000000001</v>
       </c>
-      <c r="AB173" s="7">
+      <c r="AB173">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>304.20044999999993</v>
       </c>
@@ -30543,15 +30544,15 @@
       <c r="Y174">
         <v>25</v>
       </c>
-      <c r="Z174" s="7">
+      <c r="Z174">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>42.393599999999999</v>
       </c>
-      <c r="AA174" s="7">
+      <c r="AA174">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>15.94176</v>
       </c>
-      <c r="AB174" s="7">
+      <c r="AB174">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>284.34623999999997</v>
       </c>
@@ -30640,15 +30641,15 @@
       <c r="Y175">
         <v>25</v>
       </c>
-      <c r="Z175" s="7">
+      <c r="Z175">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.945349999999998</v>
       </c>
-      <c r="AA175" s="7">
+      <c r="AA175">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>15.04458</v>
       </c>
-      <c r="AB175" s="7">
+      <c r="AB175">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>278.56128000000001</v>
       </c>
@@ -30737,15 +30738,15 @@
       <c r="Y176">
         <v>25</v>
       </c>
-      <c r="Z176" s="7">
+      <c r="Z176">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA176" s="7">
+      <c r="AA176">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB176" s="7">
+      <c r="AB176">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -30834,15 +30835,15 @@
       <c r="Y177">
         <v>26</v>
       </c>
-      <c r="Z177" s="7">
+      <c r="Z177">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA177" s="7">
+      <c r="AA177">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB177" s="7">
+      <c r="AB177">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -30931,15 +30932,15 @@
       <c r="Y178">
         <v>26</v>
       </c>
-      <c r="Z178" s="7">
+      <c r="Z178">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.608700000000002</v>
       </c>
-      <c r="AA178" s="7">
+      <c r="AA178">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.30874</v>
       </c>
-      <c r="AB178" s="7">
+      <c r="AB178">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>282.80052000000001</v>
       </c>
@@ -31028,15 +31029,15 @@
       <c r="Y179">
         <v>26</v>
       </c>
-      <c r="Z179" s="7">
+      <c r="Z179">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>12.751299999999999</v>
       </c>
-      <c r="AA179" s="7">
+      <c r="AA179">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>3.3856899999999999</v>
       </c>
-      <c r="AB179" s="7">
+      <c r="AB179">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>239.02091999999999</v>
       </c>
@@ -31125,15 +31126,15 @@
       <c r="Y180">
         <v>26</v>
       </c>
-      <c r="Z180" s="7">
+      <c r="Z180">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>23.16825</v>
       </c>
-      <c r="AA180" s="7">
+      <c r="AA180">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>15.22485</v>
       </c>
-      <c r="AB180" s="7">
+      <c r="AB180">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>267.86910000000006</v>
       </c>
@@ -31222,15 +31223,15 @@
       <c r="Y181">
         <v>26</v>
       </c>
-      <c r="Z181" s="7">
+      <c r="Z181">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>40.759680000000003</v>
       </c>
-      <c r="AA181" s="7">
+      <c r="AA181">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.537279999999999</v>
       </c>
-      <c r="AB181" s="7">
+      <c r="AB181">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.82496000000003</v>
       </c>
@@ -31319,15 +31320,15 @@
       <c r="Y182">
         <v>26</v>
       </c>
-      <c r="Z182" s="7">
+      <c r="Z182">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>46.914919999999995</v>
       </c>
-      <c r="AA182" s="7">
+      <c r="AA182">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>39.914639999999999</v>
       </c>
-      <c r="AB182" s="7">
+      <c r="AB182">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>306.05572000000001</v>
       </c>
@@ -31416,15 +31417,15 @@
       <c r="Y183">
         <v>26</v>
       </c>
-      <c r="Z183" s="7">
+      <c r="Z183">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA183" s="7">
+      <c r="AA183">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB183" s="7">
+      <c r="AB183">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -31513,15 +31514,15 @@
       <c r="Y184">
         <v>27</v>
       </c>
-      <c r="Z184" s="7">
+      <c r="Z184">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA184" s="7">
+      <c r="AA184">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB184" s="7">
+      <c r="AB184">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -31610,15 +31611,15 @@
       <c r="Y185">
         <v>27</v>
       </c>
-      <c r="Z185" s="7">
+      <c r="Z185">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.494639999999997</v>
       </c>
-      <c r="AA185" s="7">
+      <c r="AA185">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.067599999999999</v>
       </c>
-      <c r="AB185" s="7">
+      <c r="AB185">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>294.76440000000002</v>
       </c>
@@ -31707,15 +31708,15 @@
       <c r="Y186">
         <v>27</v>
       </c>
-      <c r="Z186" s="7">
+      <c r="Z186">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.361619999999995</v>
       </c>
-      <c r="AA186" s="7">
+      <c r="AA186">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.196300000000001</v>
       </c>
-      <c r="AB186" s="7">
+      <c r="AB186">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.05516</v>
       </c>
@@ -31804,15 +31805,15 @@
       <c r="Y187">
         <v>27</v>
       </c>
-      <c r="Z187" s="7">
+      <c r="Z187">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.739080000000001</v>
       </c>
-      <c r="AA187" s="7">
+      <c r="AA187">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>20.585550000000001</v>
       </c>
-      <c r="AB187" s="7">
+      <c r="AB187">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>270.79959000000002</v>
       </c>
@@ -31901,15 +31902,15 @@
       <c r="Y188">
         <v>27</v>
       </c>
-      <c r="Z188" s="7">
+      <c r="Z188">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>40.113379999999999</v>
       </c>
-      <c r="AA188" s="7">
+      <c r="AA188">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.003</v>
       </c>
-      <c r="AB188" s="7">
+      <c r="AB188">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>297.12458000000004</v>
       </c>
@@ -31998,15 +31999,15 @@
       <c r="Y189">
         <v>27</v>
       </c>
-      <c r="Z189" s="7">
+      <c r="Z189">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>25.476660000000003</v>
       </c>
-      <c r="AA189" s="7">
+      <c r="AA189">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>19.3005</v>
       </c>
-      <c r="AB189" s="7">
+      <c r="AB189">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>262.52969000000002</v>
       </c>
@@ -32095,15 +32096,15 @@
       <c r="Y190">
         <v>27</v>
       </c>
-      <c r="Z190" s="7">
+      <c r="Z190">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA190" s="7">
+      <c r="AA190">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB190" s="7">
+      <c r="AB190">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -32192,15 +32193,15 @@
       <c r="Y191">
         <v>28</v>
       </c>
-      <c r="Z191" s="7">
+      <c r="Z191">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA191" s="7">
+      <c r="AA191">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB191" s="7">
+      <c r="AB191">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -32289,15 +32290,15 @@
       <c r="Y192">
         <v>28</v>
       </c>
-      <c r="Z192" s="7">
+      <c r="Z192">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.688870000000001</v>
       </c>
-      <c r="AA192" s="7">
+      <c r="AA192">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.037410000000001</v>
       </c>
-      <c r="AB192" s="7">
+      <c r="AB192">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>296.07996999999995</v>
       </c>
@@ -32386,15 +32387,15 @@
       <c r="Y193">
         <v>28</v>
       </c>
-      <c r="Z193" s="7">
+      <c r="Z193">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.131999999999998</v>
       </c>
-      <c r="AA193" s="7">
+      <c r="AA193">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>32.131999999999998</v>
       </c>
-      <c r="AB193" s="7">
+      <c r="AB193">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>283.16048000000001</v>
       </c>
@@ -32483,15 +32484,15 @@
       <c r="Y194">
         <v>28</v>
       </c>
-      <c r="Z194" s="7">
+      <c r="Z194">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>38.923799999999993</v>
       </c>
-      <c r="AA194" s="7">
+      <c r="AA194">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.081</v>
       </c>
-      <c r="AB194" s="7">
+      <c r="AB194">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>297.29730000000001</v>
       </c>
@@ -32580,15 +32581,15 @@
       <c r="Y195">
         <v>28</v>
       </c>
-      <c r="Z195" s="7">
+      <c r="Z195">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>46.892180000000003</v>
       </c>
-      <c r="AA195" s="7">
+      <c r="AA195">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>39.315909999999995</v>
       </c>
-      <c r="AB195" s="7">
+      <c r="AB195">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>320.44484</v>
       </c>
@@ -32677,15 +32678,15 @@
       <c r="Y196">
         <v>28</v>
       </c>
-      <c r="Z196" s="7">
+      <c r="Z196">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.978439999999992</v>
       </c>
-      <c r="AA196" s="7">
+      <c r="AA196">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.898910000000001</v>
       </c>
-      <c r="AB196" s="7">
+      <c r="AB196">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>319.88385</v>
       </c>
@@ -32774,15 +32775,15 @@
       <c r="Y197">
         <v>28</v>
       </c>
-      <c r="Z197" s="7">
+      <c r="Z197">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA197" s="7">
+      <c r="AA197">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB197" s="7">
+      <c r="AB197">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -32871,15 +32872,15 @@
       <c r="Y198">
         <v>29</v>
       </c>
-      <c r="Z198" s="7">
+      <c r="Z198">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA198" s="7">
+      <c r="AA198">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB198" s="7">
+      <c r="AB198">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -32968,15 +32969,15 @@
       <c r="Y199">
         <v>29</v>
       </c>
-      <c r="Z199" s="7">
+      <c r="Z199">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.476800000000001</v>
       </c>
-      <c r="AA199" s="7">
+      <c r="AA199">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.813700000000001</v>
       </c>
-      <c r="AB199" s="7">
+      <c r="AB199">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>263.5317</v>
       </c>
@@ -33065,15 +33066,15 @@
       <c r="Y200">
         <v>29</v>
       </c>
-      <c r="Z200" s="7">
+      <c r="Z200">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.431560000000005</v>
       </c>
-      <c r="AA200" s="7">
+      <c r="AA200">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.15259</v>
       </c>
-      <c r="AB200" s="7">
+      <c r="AB200">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>294.11373000000003</v>
       </c>
@@ -33162,15 +33163,15 @@
       <c r="Y201">
         <v>29</v>
       </c>
-      <c r="Z201" s="7">
+      <c r="Z201">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.121380000000002</v>
       </c>
-      <c r="AA201" s="7">
+      <c r="AA201">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>21.907019999999999</v>
       </c>
-      <c r="AB201" s="7">
+      <c r="AB201">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>277.44493</v>
       </c>
@@ -33259,15 +33260,15 @@
       <c r="Y202">
         <v>29</v>
       </c>
-      <c r="Z202" s="7">
+      <c r="Z202">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.320820000000001</v>
       </c>
-      <c r="AA202" s="7">
+      <c r="AA202">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.451540000000001</v>
       </c>
-      <c r="AB202" s="7">
+      <c r="AB202">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>288.97889999999995</v>
       </c>
@@ -33356,15 +33357,15 @@
       <c r="Y203">
         <v>29</v>
       </c>
-      <c r="Z203" s="7">
+      <c r="Z203">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>25.994520000000001</v>
       </c>
-      <c r="AA203" s="7">
+      <c r="AA203">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.37792</v>
       </c>
-      <c r="AB203" s="7">
+      <c r="AB203">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>247.33134000000001</v>
       </c>
@@ -33453,15 +33454,15 @@
       <c r="Y204">
         <v>29</v>
       </c>
-      <c r="Z204" s="7">
+      <c r="Z204">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA204" s="7">
+      <c r="AA204">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB204" s="7">
+      <c r="AB204">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -33550,15 +33551,15 @@
       <c r="Y205">
         <v>30</v>
       </c>
-      <c r="Z205" s="7">
+      <c r="Z205">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA205" s="7">
+      <c r="AA205">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB205" s="7">
+      <c r="AB205">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -33647,15 +33648,15 @@
       <c r="Y206">
         <v>30</v>
       </c>
-      <c r="Z206" s="7">
+      <c r="Z206">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>30.662520000000001</v>
       </c>
-      <c r="AA206" s="7">
+      <c r="AA206">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.858890000000002</v>
       </c>
-      <c r="AB206" s="7">
+      <c r="AB206">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.62324000000007</v>
       </c>
@@ -33744,15 +33745,15 @@
       <c r="Y207">
         <v>30</v>
       </c>
-      <c r="Z207" s="7">
+      <c r="Z207">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.657489999999999</v>
       </c>
-      <c r="AA207" s="7">
+      <c r="AA207">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.320700000000002</v>
       </c>
-      <c r="AB207" s="7">
+      <c r="AB207">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>273.48200000000003</v>
       </c>
@@ -33841,15 +33842,15 @@
       <c r="Y208">
         <v>30</v>
       </c>
-      <c r="Z208" s="7">
+      <c r="Z208">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.02488</v>
       </c>
-      <c r="AA208" s="7">
+      <c r="AA208">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.15766</v>
       </c>
-      <c r="AB208" s="7">
+      <c r="AB208">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>274.41199999999998</v>
       </c>
@@ -33938,15 +33939,15 @@
       <c r="Y209">
         <v>30</v>
       </c>
-      <c r="Z209" s="7">
+      <c r="Z209">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.442360000000001</v>
       </c>
-      <c r="AA209" s="7">
+      <c r="AA209">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.5032</v>
       </c>
-      <c r="AB209" s="7">
+      <c r="AB209">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>282.79500000000002</v>
       </c>
@@ -34035,15 +34036,15 @@
       <c r="Y210">
         <v>30</v>
       </c>
-      <c r="Z210" s="7">
+      <c r="Z210">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.977010000000003</v>
       </c>
-      <c r="AA210" s="7">
+      <c r="AA210">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>13.971319999999999</v>
       </c>
-      <c r="AB210" s="7">
+      <c r="AB210">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>193.21841000000001</v>
       </c>
@@ -34132,15 +34133,15 @@
       <c r="Y211">
         <v>30</v>
       </c>
-      <c r="Z211" s="7">
+      <c r="Z211">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA211" s="7">
+      <c r="AA211">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB211" s="7">
+      <c r="AB211">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -34229,15 +34230,15 @@
       <c r="Y212">
         <v>31</v>
       </c>
-      <c r="Z212" s="7">
+      <c r="Z212">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA212" s="7">
+      <c r="AA212">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB212" s="7">
+      <c r="AB212">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -34326,15 +34327,15 @@
       <c r="Y213">
         <v>31</v>
       </c>
-      <c r="Z213" s="7">
+      <c r="Z213">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.808780000000002</v>
       </c>
-      <c r="AA213" s="7">
+      <c r="AA213">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>35.58746</v>
       </c>
-      <c r="AB213" s="7">
+      <c r="AB213">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>290.31172000000004</v>
       </c>
@@ -34423,15 +34424,15 @@
       <c r="Y214">
         <v>31</v>
       </c>
-      <c r="Z214" s="7">
+      <c r="Z214">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>17.272959999999998</v>
       </c>
-      <c r="AA214" s="7">
+      <c r="AA214">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>14.33568</v>
       </c>
-      <c r="AB214" s="7">
+      <c r="AB214">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>255.63104000000001</v>
       </c>
@@ -34520,15 +34521,15 @@
       <c r="Y215">
         <v>31</v>
       </c>
-      <c r="Z215" s="7">
+      <c r="Z215">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.139110000000002</v>
       </c>
-      <c r="AA215" s="7">
+      <c r="AA215">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.438179999999996</v>
       </c>
-      <c r="AB215" s="7">
+      <c r="AB215">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>276.26411999999999</v>
       </c>
@@ -34617,15 +34618,15 @@
       <c r="Y216">
         <v>31</v>
       </c>
-      <c r="Z216" s="7">
+      <c r="Z216">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>41.375700000000002</v>
       </c>
-      <c r="AA216" s="7">
+      <c r="AA216">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.407890000000002</v>
       </c>
-      <c r="AB216" s="7">
+      <c r="AB216">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>304.08914999999996</v>
       </c>
@@ -34714,15 +34715,15 @@
       <c r="Y217">
         <v>31</v>
       </c>
-      <c r="Z217" s="7">
+      <c r="Z217">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.683599999999998</v>
       </c>
-      <c r="AA217" s="7">
+      <c r="AA217">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>41.938199999999995</v>
       </c>
-      <c r="AB217" s="7">
+      <c r="AB217">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>332.06140000000005</v>
       </c>
@@ -34811,15 +34812,15 @@
       <c r="Y218">
         <v>31</v>
       </c>
-      <c r="Z218" s="7">
+      <c r="Z218">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA218" s="7">
+      <c r="AA218">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB218" s="7">
+      <c r="AB218">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -34908,15 +34909,15 @@
       <c r="Y219">
         <v>32</v>
       </c>
-      <c r="Z219" s="7">
+      <c r="Z219">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA219" s="7">
+      <c r="AA219">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB219" s="7">
+      <c r="AB219">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -35005,15 +35006,15 @@
       <c r="Y220">
         <v>32</v>
       </c>
-      <c r="Z220" s="7">
+      <c r="Z220">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.684419999999996</v>
       </c>
-      <c r="AA220" s="7">
+      <c r="AA220">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.09544</v>
       </c>
-      <c r="AB220" s="7">
+      <c r="AB220">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>287.93743999999998</v>
       </c>
@@ -35102,15 +35103,15 @@
       <c r="Y221">
         <v>32</v>
       </c>
-      <c r="Z221" s="7">
+      <c r="Z221">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.577400000000004</v>
       </c>
-      <c r="AA221" s="7">
+      <c r="AA221">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.775320000000001</v>
       </c>
-      <c r="AB221" s="7">
+      <c r="AB221">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>290.27284000000003</v>
       </c>
@@ -35199,15 +35200,15 @@
       <c r="Y222">
         <v>32</v>
       </c>
-      <c r="Z222" s="7">
+      <c r="Z222">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.551610000000004</v>
       </c>
-      <c r="AA222" s="7">
+      <c r="AA222">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.272369999999999</v>
       </c>
-      <c r="AB222" s="7">
+      <c r="AB222">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>291.40949999999998</v>
       </c>
@@ -35296,15 +35297,15 @@
       <c r="Y223">
         <v>32</v>
       </c>
-      <c r="Z223" s="7">
+      <c r="Z223">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.335039999999999</v>
       </c>
-      <c r="AA223" s="7">
+      <c r="AA223">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.658540000000002</v>
       </c>
-      <c r="AB223" s="7">
+      <c r="AB223">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>282.32693</v>
       </c>
@@ -35393,15 +35394,15 @@
       <c r="Y224">
         <v>32</v>
       </c>
-      <c r="Z224" s="7">
+      <c r="Z224">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.047199999999997</v>
       </c>
-      <c r="AA224" s="7">
+      <c r="AA224">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.689299999999999</v>
       </c>
-      <c r="AB224" s="7">
+      <c r="AB224">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>265.44099999999997</v>
       </c>
@@ -35490,15 +35491,15 @@
       <c r="Y225">
         <v>32</v>
       </c>
-      <c r="Z225" s="7">
+      <c r="Z225">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA225" s="7">
+      <c r="AA225">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB225" s="7">
+      <c r="AB225">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -35587,15 +35588,15 @@
       <c r="Y226">
         <v>33</v>
       </c>
-      <c r="Z226" s="7">
+      <c r="Z226">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA226" s="7">
+      <c r="AA226">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB226" s="7">
+      <c r="AB226">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -35684,15 +35685,15 @@
       <c r="Y227">
         <v>33</v>
       </c>
-      <c r="Z227" s="7">
+      <c r="Z227">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>46.968600000000009</v>
       </c>
-      <c r="AA227" s="7">
+      <c r="AA227">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>32.677680000000002</v>
       </c>
-      <c r="AB227" s="7">
+      <c r="AB227">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>306.43115999999998</v>
       </c>
@@ -35781,15 +35782,15 @@
       <c r="Y228">
         <v>33</v>
       </c>
-      <c r="Z228" s="7">
+      <c r="Z228">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>55.667929999999998</v>
       </c>
-      <c r="AA228" s="7">
+      <c r="AA228">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.561210000000003</v>
       </c>
-      <c r="AB228" s="7">
+      <c r="AB228">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>318.18522999999999</v>
       </c>
@@ -35878,15 +35879,15 @@
       <c r="Y229">
         <v>33</v>
       </c>
-      <c r="Z229" s="7">
+      <c r="Z229">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.536000000000001</v>
       </c>
-      <c r="AA229" s="7">
+      <c r="AA229">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>17.856839999999998</v>
       </c>
-      <c r="AB229" s="7">
+      <c r="AB229">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>284.33242000000007</v>
       </c>
@@ -35975,15 +35976,15 @@
       <c r="Y230">
         <v>33</v>
       </c>
-      <c r="Z230" s="7">
+      <c r="Z230">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.759819999999998</v>
       </c>
-      <c r="AA230" s="7">
+      <c r="AA230">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.451540000000001</v>
       </c>
-      <c r="AB230" s="7">
+      <c r="AB230">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>289.4228</v>
       </c>
@@ -36072,15 +36073,15 @@
       <c r="Y231">
         <v>33</v>
       </c>
-      <c r="Z231" s="7">
+      <c r="Z231">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>50.557740000000003</v>
       </c>
-      <c r="AA231" s="7">
+      <c r="AA231">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>35.765099999999997</v>
       </c>
-      <c r="AB231" s="7">
+      <c r="AB231">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>340.96062000000001</v>
       </c>
@@ -36169,15 +36170,15 @@
       <c r="Y232">
         <v>33</v>
       </c>
-      <c r="Z232" s="7">
+      <c r="Z232">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA232" s="7">
+      <c r="AA232">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB232" s="7">
+      <c r="AB232">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -36266,15 +36267,15 @@
       <c r="Y233">
         <v>34</v>
       </c>
-      <c r="Z233" s="7">
+      <c r="Z233">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA233" s="7">
+      <c r="AA233">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB233" s="7">
+      <c r="AB233">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -36363,15 +36364,15 @@
       <c r="Y234">
         <v>34</v>
       </c>
-      <c r="Z234" s="7">
+      <c r="Z234">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.6233</v>
       </c>
-      <c r="AA234" s="7">
+      <c r="AA234">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>19.337949999999996</v>
       </c>
-      <c r="AB234" s="7">
+      <c r="AB234">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>277.60310000000004</v>
       </c>
@@ -36460,15 +36461,15 @@
       <c r="Y235">
         <v>34</v>
       </c>
-      <c r="Z235" s="7">
+      <c r="Z235">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.775889999999997</v>
       </c>
-      <c r="AA235" s="7">
+      <c r="AA235">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.190100000000001</v>
       </c>
-      <c r="AB235" s="7">
+      <c r="AB235">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>291.55351999999999</v>
       </c>
@@ -36557,15 +36558,15 @@
       <c r="Y236">
         <v>34</v>
       </c>
-      <c r="Z236" s="7">
+      <c r="Z236">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.143479999999997</v>
       </c>
-      <c r="AA236" s="7">
+      <c r="AA236">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>34.833120000000001</v>
       </c>
-      <c r="AB236" s="7">
+      <c r="AB236">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>299.68035000000003</v>
       </c>
@@ -36654,15 +36655,15 @@
       <c r="Y237">
         <v>34</v>
       </c>
-      <c r="Z237" s="7">
+      <c r="Z237">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.381540000000001</v>
       </c>
-      <c r="AA237" s="7">
+      <c r="AA237">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.689610000000002</v>
       </c>
-      <c r="AB237" s="7">
+      <c r="AB237">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>276.55884000000003</v>
       </c>
@@ -36751,15 +36752,15 @@
       <c r="Y238">
         <v>34</v>
       </c>
-      <c r="Z238" s="7">
+      <c r="Z238">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.308130000000002</v>
       </c>
-      <c r="AA238" s="7">
+      <c r="AA238">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.061430000000001</v>
       </c>
-      <c r="AB238" s="7">
+      <c r="AB238">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>236.99445</v>
       </c>
@@ -36848,15 +36849,15 @@
       <c r="Y239">
         <v>34</v>
       </c>
-      <c r="Z239" s="7">
+      <c r="Z239">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA239" s="7">
+      <c r="AA239">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB239" s="7">
+      <c r="AB239">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -36945,15 +36946,15 @@
       <c r="Y240">
         <v>35</v>
       </c>
-      <c r="Z240" s="7">
+      <c r="Z240">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA240" s="7">
+      <c r="AA240">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB240" s="7">
+      <c r="AB240">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -37042,15 +37043,15 @@
       <c r="Y241">
         <v>35</v>
       </c>
-      <c r="Z241" s="7">
+      <c r="Z241">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.731249999999999</v>
       </c>
-      <c r="AA241" s="7">
+      <c r="AA241">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>18.147329999999997</v>
       </c>
-      <c r="AB241" s="7">
+      <c r="AB241">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>272.96424000000002</v>
       </c>
@@ -37139,15 +37140,15 @@
       <c r="Y242">
         <v>35</v>
       </c>
-      <c r="Z242" s="7">
+      <c r="Z242">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>45.015699999999995</v>
       </c>
-      <c r="AA242" s="7">
+      <c r="AA242">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.549910000000001</v>
       </c>
-      <c r="AB242" s="7">
+      <c r="AB242">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>298.57443000000001</v>
       </c>
@@ -37236,15 +37237,15 @@
       <c r="Y243">
         <v>35</v>
       </c>
-      <c r="Z243" s="7">
+      <c r="Z243">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.899099999999997</v>
       </c>
-      <c r="AA243" s="7">
+      <c r="AA243">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>34.103700000000003</v>
       </c>
-      <c r="AB243" s="7">
+      <c r="AB243">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>305.64047999999997</v>
       </c>
@@ -37333,15 +37334,15 @@
       <c r="Y244">
         <v>35</v>
       </c>
-      <c r="Z244" s="7">
+      <c r="Z244">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>38.074880000000007</v>
       </c>
-      <c r="AA244" s="7">
+      <c r="AA244">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>32.425920000000005</v>
       </c>
-      <c r="AB244" s="7">
+      <c r="AB244">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>297.92704000000003</v>
       </c>
@@ -37430,15 +37431,15 @@
       <c r="Y245">
         <v>35</v>
       </c>
-      <c r="Z245" s="7">
+      <c r="Z245">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.750360000000001</v>
       </c>
-      <c r="AA245" s="7">
+      <c r="AA245">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.176159999999999</v>
       </c>
-      <c r="AB245" s="7">
+      <c r="AB245">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>287.10032000000001</v>
       </c>
@@ -37527,15 +37528,15 @@
       <c r="Y246">
         <v>35</v>
       </c>
-      <c r="Z246" s="7">
+      <c r="Z246">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA246" s="7">
+      <c r="AA246">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB246" s="7">
+      <c r="AB246">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -37624,15 +37625,15 @@
       <c r="Y247">
         <v>36</v>
       </c>
-      <c r="Z247" s="7">
+      <c r="Z247">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA247" s="7">
+      <c r="AA247">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB247" s="7">
+      <c r="AB247">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -37721,15 +37722,15 @@
       <c r="Y248">
         <v>36</v>
       </c>
-      <c r="Z248" s="7">
+      <c r="Z248">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.264919999999996</v>
       </c>
-      <c r="AA248" s="7">
+      <c r="AA248">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.7288</v>
       </c>
-      <c r="AB248" s="7">
+      <c r="AB248">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.25508000000002</v>
       </c>
@@ -37818,15 +37819,15 @@
       <c r="Y249">
         <v>36</v>
       </c>
-      <c r="Z249" s="7">
+      <c r="Z249">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.516199999999998</v>
       </c>
-      <c r="AA249" s="7">
+      <c r="AA249">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.9344</v>
       </c>
-      <c r="AB249" s="7">
+      <c r="AB249">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>283.60859999999997</v>
       </c>
@@ -37915,15 +37916,15 @@
       <c r="Y250">
         <v>36</v>
       </c>
-      <c r="Z250" s="7">
+      <c r="Z250">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.571400000000001</v>
       </c>
-      <c r="AA250" s="7">
+      <c r="AA250">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.391219999999997</v>
       </c>
-      <c r="AB250" s="7">
+      <c r="AB250">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>272.73451</v>
       </c>
@@ -38012,15 +38013,15 @@
       <c r="Y251">
         <v>36</v>
       </c>
-      <c r="Z251" s="7">
+      <c r="Z251">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>40.085999999999999</v>
       </c>
-      <c r="AA251" s="7">
+      <c r="AA251">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.752719999999997</v>
       </c>
-      <c r="AB251" s="7">
+      <c r="AB251">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>294.49848000000003</v>
       </c>
@@ -38109,15 +38110,15 @@
       <c r="Y252">
         <v>36</v>
       </c>
-      <c r="Z252" s="7">
+      <c r="Z252">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.235520000000001</v>
       </c>
-      <c r="AA252" s="7">
+      <c r="AA252">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>20.686439999999997</v>
       </c>
-      <c r="AB252" s="7">
+      <c r="AB252">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>302.20830000000001</v>
       </c>
@@ -38206,15 +38207,15 @@
       <c r="Y253">
         <v>36</v>
       </c>
-      <c r="Z253" s="7">
+      <c r="Z253">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA253" s="7">
+      <c r="AA253">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB253" s="7">
+      <c r="AB253">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -38303,15 +38304,15 @@
       <c r="Y254">
         <v>37</v>
       </c>
-      <c r="Z254" s="7">
+      <c r="Z254">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA254" s="7">
+      <c r="AA254">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB254" s="7">
+      <c r="AB254">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -38400,15 +38401,15 @@
       <c r="Y255">
         <v>37</v>
       </c>
-      <c r="Z255" s="7">
+      <c r="Z255">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.491</v>
       </c>
-      <c r="AA255" s="7">
+      <c r="AA255">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.537500000000001</v>
       </c>
-      <c r="AB255" s="7">
+      <c r="AB255">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>265.3938</v>
       </c>
@@ -38497,15 +38498,15 @@
       <c r="Y256">
         <v>37</v>
       </c>
-      <c r="Z256" s="7">
+      <c r="Z256">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.87576</v>
       </c>
-      <c r="AA256" s="7">
+      <c r="AA256">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.411519999999999</v>
       </c>
-      <c r="AB256" s="7">
+      <c r="AB256">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>281.73635999999999</v>
       </c>
@@ -38594,15 +38595,15 @@
       <c r="Y257">
         <v>37</v>
       </c>
-      <c r="Z257" s="7">
+      <c r="Z257">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.207599999999999</v>
       </c>
-      <c r="AA257" s="7">
+      <c r="AA257">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>34.0884</v>
       </c>
-      <c r="AB257" s="7">
+      <c r="AB257">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>304.30024000000003</v>
       </c>
@@ -38691,15 +38692,15 @@
       <c r="Y258">
         <v>37</v>
       </c>
-      <c r="Z258" s="7">
+      <c r="Z258">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.4758</v>
       </c>
-      <c r="AA258" s="7">
+      <c r="AA258">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>28.588600000000003</v>
       </c>
-      <c r="AB258" s="7">
+      <c r="AB258">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>293.95859999999999</v>
       </c>
@@ -38788,15 +38789,15 @@
       <c r="Y259">
         <v>37</v>
       </c>
-      <c r="Z259" s="7">
+      <c r="Z259">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.240069999999996</v>
       </c>
-      <c r="AA259" s="7">
+      <c r="AA259">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>41.82423</v>
       </c>
-      <c r="AB259" s="7">
+      <c r="AB259">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>344.25720000000001</v>
       </c>
@@ -38885,15 +38886,15 @@
       <c r="Y260">
         <v>37</v>
       </c>
-      <c r="Z260" s="7">
+      <c r="Z260">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA260" s="7">
+      <c r="AA260">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB260" s="7">
+      <c r="AB260">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -38982,15 +38983,15 @@
       <c r="Y261">
         <v>38</v>
       </c>
-      <c r="Z261" s="7">
+      <c r="Z261">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA261" s="7">
+      <c r="AA261">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB261" s="7">
+      <c r="AB261">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -39079,15 +39080,15 @@
       <c r="Y262">
         <v>38</v>
       </c>
-      <c r="Z262" s="7">
+      <c r="Z262">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.133600000000008</v>
       </c>
-      <c r="AA262" s="7">
+      <c r="AA262">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.883839999999999</v>
       </c>
-      <c r="AB262" s="7">
+      <c r="AB262">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>299.41651000000002</v>
       </c>
@@ -39176,15 +39177,15 @@
       <c r="Y263">
         <v>38</v>
       </c>
-      <c r="Z263" s="7">
+      <c r="Z263">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.755199999999995</v>
       </c>
-      <c r="AA263" s="7">
+      <c r="AA263">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.6572</v>
       </c>
-      <c r="AB263" s="7">
+      <c r="AB263">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>302.98559999999998</v>
       </c>
@@ -39273,15 +39274,15 @@
       <c r="Y264">
         <v>38</v>
       </c>
-      <c r="Z264" s="7">
+      <c r="Z264">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>49.706580000000002</v>
       </c>
-      <c r="AA264" s="7">
+      <c r="AA264">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>35.370719999999999</v>
       </c>
-      <c r="AB264" s="7">
+      <c r="AB264">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>318.20249999999999</v>
       </c>
@@ -39370,15 +39371,15 @@
       <c r="Y265">
         <v>38</v>
       </c>
-      <c r="Z265" s="7">
+      <c r="Z265">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>51.403659999999995</v>
       </c>
-      <c r="AA265" s="7">
+      <c r="AA265">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.80762</v>
       </c>
-      <c r="AB265" s="7">
+      <c r="AB265">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>308.24331999999998</v>
       </c>
@@ -39467,15 +39468,15 @@
       <c r="Y266">
         <v>38</v>
       </c>
-      <c r="Z266" s="7">
+      <c r="Z266">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.510239999999996</v>
       </c>
-      <c r="AA266" s="7">
+      <c r="AA266">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>38.940799999999996</v>
       </c>
-      <c r="AB266" s="7">
+      <c r="AB266">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>316.32607999999999</v>
       </c>
@@ -39564,15 +39565,15 @@
       <c r="Y267">
         <v>38</v>
       </c>
-      <c r="Z267" s="7">
+      <c r="Z267">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA267" s="7">
+      <c r="AA267">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB267" s="7">
+      <c r="AB267">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -39661,15 +39662,15 @@
       <c r="Y268">
         <v>39</v>
       </c>
-      <c r="Z268" s="7">
+      <c r="Z268">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA268" s="7">
+      <c r="AA268">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB268" s="7">
+      <c r="AB268">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -39758,15 +39759,15 @@
       <c r="Y269">
         <v>39</v>
       </c>
-      <c r="Z269" s="7">
+      <c r="Z269">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.17502</v>
       </c>
-      <c r="AA269" s="7">
+      <c r="AA269">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>28.690999999999999</v>
       </c>
-      <c r="AB269" s="7">
+      <c r="AB269">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>275.96328000000005</v>
       </c>
@@ -39855,15 +39856,15 @@
       <c r="Y270">
         <v>39</v>
       </c>
-      <c r="Z270" s="7">
+      <c r="Z270">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.341999999999999</v>
       </c>
-      <c r="AA270" s="7">
+      <c r="AA270">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.224799999999998</v>
       </c>
-      <c r="AB270" s="7">
+      <c r="AB270">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>291.10419999999993</v>
       </c>
@@ -39952,15 +39953,15 @@
       <c r="Y271">
         <v>39</v>
       </c>
-      <c r="Z271" s="7">
+      <c r="Z271">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>16.219200000000001</v>
       </c>
-      <c r="AA271" s="7">
+      <c r="AA271">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>6.8016000000000005</v>
       </c>
-      <c r="AB271" s="7">
+      <c r="AB271">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>249.04319999999998</v>
       </c>
@@ -40049,15 +40050,15 @@
       <c r="Y272">
         <v>39</v>
       </c>
-      <c r="Z272" s="7">
+      <c r="Z272">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>28.409939999999999</v>
       </c>
-      <c r="AA272" s="7">
+      <c r="AA272">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>19.651319999999998</v>
       </c>
-      <c r="AB272" s="7">
+      <c r="AB272">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>274.00698000000006</v>
       </c>
@@ -40146,15 +40147,15 @@
       <c r="Y273">
         <v>39</v>
       </c>
-      <c r="Z273" s="7">
+      <c r="Z273">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>30.492719999999998</v>
       </c>
-      <c r="AA273" s="7">
+      <c r="AA273">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>20.602079999999997</v>
       </c>
-      <c r="AB273" s="7">
+      <c r="AB273">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>257.15663999999998</v>
       </c>
@@ -40243,15 +40244,15 @@
       <c r="Y274">
         <v>39</v>
       </c>
-      <c r="Z274" s="7">
+      <c r="Z274">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA274" s="7">
+      <c r="AA274">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB274" s="7">
+      <c r="AB274">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -40340,15 +40341,15 @@
       <c r="Y275">
         <v>40</v>
       </c>
-      <c r="Z275" s="7">
+      <c r="Z275">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA275" s="7">
+      <c r="AA275">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB275" s="7">
+      <c r="AB275">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -40437,15 +40438,15 @@
       <c r="Y276">
         <v>40</v>
       </c>
-      <c r="Z276" s="7">
+      <c r="Z276">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>19.8855</v>
       </c>
-      <c r="AA276" s="7">
+      <c r="AA276">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>18.20628</v>
       </c>
-      <c r="AB276" s="7">
+      <c r="AB276">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>262.57697999999999</v>
       </c>
@@ -40534,15 +40535,15 @@
       <c r="Y277">
         <v>40</v>
       </c>
-      <c r="Z277" s="7">
+      <c r="Z277">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>20.443840000000002</v>
       </c>
-      <c r="AA277" s="7">
+      <c r="AA277">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.338420000000003</v>
       </c>
-      <c r="AB277" s="7">
+      <c r="AB277">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>265.63774000000001</v>
       </c>
@@ -40631,15 +40632,15 @@
       <c r="Y278">
         <v>40</v>
       </c>
-      <c r="Z278" s="7">
+      <c r="Z278">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>43.358249999999998</v>
       </c>
-      <c r="AA278" s="7">
+      <c r="AA278">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>32.685449999999996</v>
       </c>
-      <c r="AB278" s="7">
+      <c r="AB278">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>299.95015000000001</v>
       </c>
@@ -40728,15 +40729,15 @@
       <c r="Y279">
         <v>40</v>
       </c>
-      <c r="Z279" s="7">
+      <c r="Z279">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.045000000000002</v>
       </c>
-      <c r="AA279" s="7">
+      <c r="AA279">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>11.68385</v>
       </c>
-      <c r="AB279" s="7">
+      <c r="AB279">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>253.16478000000001</v>
       </c>
@@ -40825,15 +40826,15 @@
       <c r="Y280">
         <v>40</v>
       </c>
-      <c r="Z280" s="7">
+      <c r="Z280">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.755749999999999</v>
       </c>
-      <c r="AA280" s="7">
+      <c r="AA280">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>32.49</v>
       </c>
-      <c r="AB280" s="7">
+      <c r="AB280">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>279.58499999999998</v>
       </c>
@@ -40922,15 +40923,15 @@
       <c r="Y281">
         <v>40</v>
       </c>
-      <c r="Z281" s="7">
+      <c r="Z281">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA281" s="7">
+      <c r="AA281">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB281" s="7">
+      <c r="AB281">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -41019,15 +41020,15 @@
       <c r="Y282">
         <v>41</v>
       </c>
-      <c r="Z282" s="7">
+      <c r="Z282">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA282" s="7">
+      <c r="AA282">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB282" s="7">
+      <c r="AB282">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -41116,15 +41117,15 @@
       <c r="Y283">
         <v>41</v>
       </c>
-      <c r="Z283" s="7">
+      <c r="Z283">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>40.731659999999998</v>
       </c>
-      <c r="AA283" s="7">
+      <c r="AA283">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>23.737949999999998</v>
       </c>
-      <c r="AB283" s="7">
+      <c r="AB283">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>291.82148999999998</v>
       </c>
@@ -41213,15 +41214,15 @@
       <c r="Y284">
         <v>41</v>
       </c>
-      <c r="Z284" s="7">
+      <c r="Z284">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>46.630319999999998</v>
       </c>
-      <c r="AA284" s="7">
+      <c r="AA284">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.974160000000005</v>
       </c>
-      <c r="AB284" s="7">
+      <c r="AB284">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>311.55696</v>
       </c>
@@ -41310,15 +41311,15 @@
       <c r="Y285">
         <v>41</v>
       </c>
-      <c r="Z285" s="7">
+      <c r="Z285">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.401000000000003</v>
       </c>
-      <c r="AA285" s="7">
+      <c r="AA285">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.433</v>
       </c>
-      <c r="AB285" s="7">
+      <c r="AB285">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>292.36500000000001</v>
       </c>
@@ -41407,15 +41408,15 @@
       <c r="Y286">
         <v>41</v>
       </c>
-      <c r="Z286" s="7">
+      <c r="Z286">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.175229999999999</v>
       </c>
-      <c r="AA286" s="7">
+      <c r="AA286">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>21.996660000000002</v>
       </c>
-      <c r="AB286" s="7">
+      <c r="AB286">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>287.67920999999996</v>
       </c>
@@ -41504,15 +41505,15 @@
       <c r="Y287">
         <v>41</v>
       </c>
-      <c r="Z287" s="7">
+      <c r="Z287">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.431650000000005</v>
       </c>
-      <c r="AA287" s="7">
+      <c r="AA287">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.544229999999999</v>
       </c>
-      <c r="AB287" s="7">
+      <c r="AB287">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>267.99309000000005</v>
       </c>
@@ -41601,15 +41602,15 @@
       <c r="Y288">
         <v>41</v>
       </c>
-      <c r="Z288" s="7">
+      <c r="Z288">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA288" s="7">
+      <c r="AA288">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB288" s="7">
+      <c r="AB288">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -41698,15 +41699,15 @@
       <c r="Y289">
         <v>42</v>
       </c>
-      <c r="Z289" s="7">
+      <c r="Z289">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA289" s="7">
+      <c r="AA289">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB289" s="7">
+      <c r="AB289">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -41795,15 +41796,15 @@
       <c r="Y290">
         <v>42</v>
       </c>
-      <c r="Z290" s="7">
+      <c r="Z290">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.993100000000005</v>
       </c>
-      <c r="AA290" s="7">
+      <c r="AA290">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.182050000000004</v>
       </c>
-      <c r="AB290" s="7">
+      <c r="AB290">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.76337999999998</v>
       </c>
@@ -41892,15 +41893,15 @@
       <c r="Y291">
         <v>42</v>
       </c>
-      <c r="Z291" s="7">
+      <c r="Z291">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>25.225829999999998</v>
       </c>
-      <c r="AA291" s="7">
+      <c r="AA291">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.761760000000002</v>
       </c>
-      <c r="AB291" s="7">
+      <c r="AB291">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>288.51764999999995</v>
       </c>
@@ -41989,15 +41990,15 @@
       <c r="Y292">
         <v>42</v>
       </c>
-      <c r="Z292" s="7">
+      <c r="Z292">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.001300000000004</v>
       </c>
-      <c r="AA292" s="7">
+      <c r="AA292">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>13.529489999999999</v>
       </c>
-      <c r="AB292" s="7">
+      <c r="AB292">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>262.48091999999997</v>
       </c>
@@ -42086,15 +42087,15 @@
       <c r="Y293">
         <v>42</v>
       </c>
-      <c r="Z293" s="7">
+      <c r="Z293">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>29.970789999999997</v>
       </c>
-      <c r="AA293" s="7">
+      <c r="AA293">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.924009999999999</v>
       </c>
-      <c r="AB293" s="7">
+      <c r="AB293">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>277.52863000000002</v>
       </c>
@@ -42183,15 +42184,15 @@
       <c r="Y294">
         <v>42</v>
       </c>
-      <c r="Z294" s="7">
+      <c r="Z294">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>53.029159999999997</v>
       </c>
-      <c r="AA294" s="7">
+      <c r="AA294">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>52.65128</v>
       </c>
-      <c r="AB294" s="7">
+      <c r="AB294">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>427.00439999999998</v>
       </c>
@@ -42280,15 +42281,15 @@
       <c r="Y295">
         <v>42</v>
       </c>
-      <c r="Z295" s="7">
+      <c r="Z295">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA295" s="7">
+      <c r="AA295">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB295" s="7">
+      <c r="AB295">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -42377,15 +42378,15 @@
       <c r="Y296">
         <v>43</v>
       </c>
-      <c r="Z296" s="7">
+      <c r="Z296">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA296" s="7">
+      <c r="AA296">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB296" s="7">
+      <c r="AB296">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -42474,15 +42475,15 @@
       <c r="Y297">
         <v>43</v>
       </c>
-      <c r="Z297" s="7">
+      <c r="Z297">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.352119999999999</v>
       </c>
-      <c r="AA297" s="7">
+      <c r="AA297">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>19.46472</v>
       </c>
-      <c r="AB297" s="7">
+      <c r="AB297">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.54912000000002</v>
       </c>
@@ -42571,15 +42572,15 @@
       <c r="Y298">
         <v>43</v>
       </c>
-      <c r="Z298" s="7">
+      <c r="Z298">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>23.64593</v>
       </c>
-      <c r="AA298" s="7">
+      <c r="AA298">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>14.871930000000001</v>
       </c>
-      <c r="AB298" s="7">
+      <c r="AB298">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>264.14127000000002</v>
       </c>
@@ -42668,15 +42669,15 @@
       <c r="Y299">
         <v>43</v>
       </c>
-      <c r="Z299" s="7">
+      <c r="Z299">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.457360000000001</v>
       </c>
-      <c r="AA299" s="7">
+      <c r="AA299">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>11.696020000000001</v>
       </c>
-      <c r="AB299" s="7">
+      <c r="AB299">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>254.10263</v>
       </c>
@@ -42765,15 +42766,15 @@
       <c r="Y300">
         <v>43</v>
       </c>
-      <c r="Z300" s="7">
+      <c r="Z300">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>47.898720000000004</v>
       </c>
-      <c r="AA300" s="7">
+      <c r="AA300">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.060959999999998</v>
       </c>
-      <c r="AB300" s="7">
+      <c r="AB300">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>303.99839999999995</v>
       </c>
@@ -42862,15 +42863,15 @@
       <c r="Y301">
         <v>43</v>
       </c>
-      <c r="Z301" s="7">
+      <c r="Z301">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.65522</v>
       </c>
-      <c r="AA301" s="7">
+      <c r="AA301">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.318490000000001</v>
       </c>
-      <c r="AB301" s="7">
+      <c r="AB301">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>324.74684000000002</v>
       </c>
@@ -42959,15 +42960,15 @@
       <c r="Y302">
         <v>43</v>
       </c>
-      <c r="Z302" s="7">
+      <c r="Z302">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA302" s="7">
+      <c r="AA302">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB302" s="7">
+      <c r="AB302">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -43056,15 +43057,15 @@
       <c r="Y303">
         <v>44</v>
       </c>
-      <c r="Z303" s="7">
+      <c r="Z303">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA303" s="7">
+      <c r="AA303">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB303" s="7">
+      <c r="AB303">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -43153,15 +43154,15 @@
       <c r="Y304">
         <v>44</v>
       </c>
-      <c r="Z304" s="7">
+      <c r="Z304">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.096360000000001</v>
       </c>
-      <c r="AA304" s="7">
+      <c r="AA304">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.34984</v>
       </c>
-      <c r="AB304" s="7">
+      <c r="AB304">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>282.70627999999999</v>
       </c>
@@ -43250,15 +43251,15 @@
       <c r="Y305">
         <v>44</v>
       </c>
-      <c r="Z305" s="7">
+      <c r="Z305">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.960209999999996</v>
       </c>
-      <c r="AA305" s="7">
+      <c r="AA305">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.601489999999998</v>
       </c>
-      <c r="AB305" s="7">
+      <c r="AB305">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>291.86586</v>
       </c>
@@ -43347,15 +43348,15 @@
       <c r="Y306">
         <v>44</v>
       </c>
-      <c r="Z306" s="7">
+      <c r="Z306">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>21.766029999999997</v>
       </c>
-      <c r="AA306" s="7">
+      <c r="AA306">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.484600000000004</v>
       </c>
-      <c r="AB306" s="7">
+      <c r="AB306">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>278.12642</v>
       </c>
@@ -43444,15 +43445,15 @@
       <c r="Y307">
         <v>44</v>
       </c>
-      <c r="Z307" s="7">
+      <c r="Z307">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>23.385120000000004</v>
       </c>
-      <c r="AA307" s="7">
+      <c r="AA307">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>18.070319999999999</v>
       </c>
-      <c r="AB307" s="7">
+      <c r="AB307">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>257.67921999999999</v>
       </c>
@@ -43541,15 +43542,15 @@
       <c r="Y308">
         <v>44</v>
       </c>
-      <c r="Z308" s="7">
+      <c r="Z308">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.603840000000005</v>
       </c>
-      <c r="AA308" s="7">
+      <c r="AA308">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>17.734079999999999</v>
       </c>
-      <c r="AB308" s="7">
+      <c r="AB308">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>276.36336</v>
       </c>
@@ -43638,15 +43639,15 @@
       <c r="Y309">
         <v>44</v>
       </c>
-      <c r="Z309" s="7">
+      <c r="Z309">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA309" s="7">
+      <c r="AA309">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB309" s="7">
+      <c r="AB309">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -43735,15 +43736,15 @@
       <c r="Y310">
         <v>45</v>
       </c>
-      <c r="Z310" s="7">
+      <c r="Z310">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA310" s="7">
+      <c r="AA310">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB310" s="7">
+      <c r="AB310">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -43832,15 +43833,15 @@
       <c r="Y311">
         <v>45</v>
       </c>
-      <c r="Z311" s="7">
+      <c r="Z311">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>19.429440000000003</v>
       </c>
-      <c r="AA311" s="7">
+      <c r="AA311">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.191200000000002</v>
       </c>
-      <c r="AB311" s="7">
+      <c r="AB311">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>259.97816</v>
       </c>
@@ -43929,15 +43930,15 @@
       <c r="Y312">
         <v>45</v>
       </c>
-      <c r="Z312" s="7">
+      <c r="Z312">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.699599999999997</v>
       </c>
-      <c r="AA312" s="7">
+      <c r="AA312">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.7288</v>
       </c>
-      <c r="AB312" s="7">
+      <c r="AB312">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>285.62520000000001</v>
       </c>
@@ -44026,15 +44027,15 @@
       <c r="Y313">
         <v>45</v>
       </c>
-      <c r="Z313" s="7">
+      <c r="Z313">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.915599999999998</v>
       </c>
-      <c r="AA313" s="7">
+      <c r="AA313">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.026350000000001</v>
       </c>
-      <c r="AB313" s="7">
+      <c r="AB313">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>295.41469999999993</v>
       </c>
@@ -44123,15 +44124,15 @@
       <c r="Y314">
         <v>45</v>
       </c>
-      <c r="Z314" s="7">
+      <c r="Z314">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>17.376480000000001</v>
       </c>
-      <c r="AA314" s="7">
+      <c r="AA314">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>16.19172</v>
       </c>
-      <c r="AB314" s="7">
+      <c r="AB314">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>257.79500000000002</v>
       </c>
@@ -44220,15 +44221,15 @@
       <c r="Y315">
         <v>45</v>
       </c>
-      <c r="Z315" s="7">
+      <c r="Z315">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.832819999999998</v>
       </c>
-      <c r="AA315" s="7">
+      <c r="AA315">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.527930000000001</v>
       </c>
-      <c r="AB315" s="7">
+      <c r="AB315">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>342.82094000000001</v>
       </c>
@@ -44317,15 +44318,15 @@
       <c r="Y316">
         <v>45</v>
       </c>
-      <c r="Z316" s="7">
+      <c r="Z316">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA316" s="7">
+      <c r="AA316">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB316" s="7">
+      <c r="AB316">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -44414,15 +44415,15 @@
       <c r="Y317">
         <v>46</v>
       </c>
-      <c r="Z317" s="7">
+      <c r="Z317">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA317" s="7">
+      <c r="AA317">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB317" s="7">
+      <c r="AB317">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -44511,15 +44512,15 @@
       <c r="Y318">
         <v>46</v>
       </c>
-      <c r="Z318" s="7">
+      <c r="Z318">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>42.813019999999995</v>
       </c>
-      <c r="AA318" s="7">
+      <c r="AA318">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.657830000000001</v>
       </c>
-      <c r="AB318" s="7">
+      <c r="AB318">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>296.16063000000003</v>
       </c>
@@ -44608,15 +44609,15 @@
       <c r="Y319">
         <v>46</v>
       </c>
-      <c r="Z319" s="7">
+      <c r="Z319">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>25.585919999999998</v>
       </c>
-      <c r="AA319" s="7">
+      <c r="AA319">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>30.33886</v>
       </c>
-      <c r="AB319" s="7">
+      <c r="AB319">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>283.31076000000002</v>
       </c>
@@ -44705,15 +44706,15 @@
       <c r="Y320">
         <v>46</v>
       </c>
-      <c r="Z320" s="7">
+      <c r="Z320">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>25.688039999999997</v>
       </c>
-      <c r="AA320" s="7">
+      <c r="AA320">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.910640000000004</v>
       </c>
-      <c r="AB320" s="7">
+      <c r="AB320">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>272.50691999999998</v>
       </c>
@@ -44802,15 +44803,15 @@
       <c r="Y321">
         <v>46</v>
       </c>
-      <c r="Z321" s="7">
+      <c r="Z321">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.835720000000002</v>
       </c>
-      <c r="AA321" s="7">
+      <c r="AA321">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>22.526010000000003</v>
       </c>
-      <c r="AB321" s="7">
+      <c r="AB321">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>276.79889999999995</v>
       </c>
@@ -44899,15 +44900,15 @@
       <c r="Y322">
         <v>46</v>
       </c>
-      <c r="Z322" s="7">
+      <c r="Z322">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.142580000000002</v>
       </c>
-      <c r="AA322" s="7">
+      <c r="AA322">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.135719999999999</v>
       </c>
-      <c r="AB322" s="7">
+      <c r="AB322">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>344.05907000000002</v>
       </c>
@@ -44996,15 +44997,15 @@
       <c r="Y323">
         <v>46</v>
       </c>
-      <c r="Z323" s="7">
+      <c r="Z323">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA323" s="7">
+      <c r="AA323">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB323" s="7">
+      <c r="AB323">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -45093,15 +45094,15 @@
       <c r="Y324">
         <v>47</v>
       </c>
-      <c r="Z324" s="7">
+      <c r="Z324">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA324" s="7">
+      <c r="AA324">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB324" s="7">
+      <c r="AB324">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -45190,15 +45191,15 @@
       <c r="Y325">
         <v>47</v>
       </c>
-      <c r="Z325" s="7">
+      <c r="Z325">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.074240000000003</v>
       </c>
-      <c r="AA325" s="7">
+      <c r="AA325">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>28.321080000000002</v>
       </c>
-      <c r="AB325" s="7">
+      <c r="AB325">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>284.27951999999999</v>
       </c>
@@ -45287,15 +45288,15 @@
       <c r="Y326">
         <v>47</v>
       </c>
-      <c r="Z326" s="7">
+      <c r="Z326">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>24.507360000000002</v>
       </c>
-      <c r="AA326" s="7">
+      <c r="AA326">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.37312</v>
       </c>
-      <c r="AB326" s="7">
+      <c r="AB326">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>279.53568000000001</v>
       </c>
@@ -45384,15 +45385,15 @@
       <c r="Y327">
         <v>47</v>
       </c>
-      <c r="Z327" s="7">
+      <c r="Z327">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.708589999999994</v>
       </c>
-      <c r="AA327" s="7">
+      <c r="AA327">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>28.276109999999999</v>
       </c>
-      <c r="AB327" s="7">
+      <c r="AB327">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>294.28595999999999</v>
       </c>
@@ -45481,15 +45482,15 @@
       <c r="Y328">
         <v>47</v>
       </c>
-      <c r="Z328" s="7">
+      <c r="Z328">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.312800000000003</v>
       </c>
-      <c r="AA328" s="7">
+      <c r="AA328">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.629239999999999</v>
       </c>
-      <c r="AB328" s="7">
+      <c r="AB328">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>289.66281999999995</v>
       </c>
@@ -45578,15 +45579,15 @@
       <c r="Y329">
         <v>47</v>
       </c>
-      <c r="Z329" s="7">
+      <c r="Z329">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.963000000000001</v>
       </c>
-      <c r="AA329" s="7">
+      <c r="AA329">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>10.179</v>
       </c>
-      <c r="AB329" s="7">
+      <c r="AB329">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>239.38200000000001</v>
       </c>
@@ -45675,15 +45676,15 @@
       <c r="Y330">
         <v>47</v>
       </c>
-      <c r="Z330" s="7">
+      <c r="Z330">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA330" s="7">
+      <c r="AA330">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB330" s="7">
+      <c r="AB330">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -45772,15 +45773,15 @@
       <c r="Y331">
         <v>48</v>
       </c>
-      <c r="Z331" s="7">
+      <c r="Z331">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA331" s="7">
+      <c r="AA331">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB331" s="7">
+      <c r="AB331">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -45869,15 +45870,15 @@
       <c r="Y332">
         <v>48</v>
       </c>
-      <c r="Z332" s="7">
+      <c r="Z332">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>48.738429999999994</v>
       </c>
-      <c r="AA332" s="7">
+      <c r="AA332">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>43.814899999999994</v>
       </c>
-      <c r="AB332" s="7">
+      <c r="AB332">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>325.94671999999997</v>
       </c>
@@ -45966,15 +45967,15 @@
       <c r="Y333">
         <v>48</v>
       </c>
-      <c r="Z333" s="7">
+      <c r="Z333">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.720759999999999</v>
       </c>
-      <c r="AA333" s="7">
+      <c r="AA333">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.794419999999999</v>
       </c>
-      <c r="AB333" s="7">
+      <c r="AB333">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>289.97936000000004</v>
       </c>
@@ -46063,15 +46064,15 @@
       <c r="Y334">
         <v>48</v>
       </c>
-      <c r="Z334" s="7">
+      <c r="Z334">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>44.020199999999996</v>
       </c>
-      <c r="AA334" s="7">
+      <c r="AA334">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>36.304400000000001</v>
       </c>
-      <c r="AB334" s="7">
+      <c r="AB334">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>308.4982</v>
       </c>
@@ -46160,15 +46161,15 @@
       <c r="Y335">
         <v>48</v>
       </c>
-      <c r="Z335" s="7">
+      <c r="Z335">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>42.256019999999999</v>
       </c>
-      <c r="AA335" s="7">
+      <c r="AA335">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.95872</v>
       </c>
-      <c r="AB335" s="7">
+      <c r="AB335">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>295.17137999999994</v>
       </c>
@@ -46257,15 +46258,15 @@
       <c r="Y336">
         <v>48</v>
       </c>
-      <c r="Z336" s="7">
+      <c r="Z336">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>33.914879999999997</v>
       </c>
-      <c r="AA336" s="7">
+      <c r="AA336">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>26.33728</v>
       </c>
-      <c r="AB336" s="7">
+      <c r="AB336">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>274.30912000000001</v>
       </c>
@@ -46354,15 +46355,15 @@
       <c r="Y337">
         <v>48</v>
       </c>
-      <c r="Z337" s="7">
+      <c r="Z337">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA337" s="7">
+      <c r="AA337">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB337" s="7">
+      <c r="AB337">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -46451,15 +46452,15 @@
       <c r="Y338">
         <v>49</v>
       </c>
-      <c r="Z338" s="7">
+      <c r="Z338">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA338" s="7">
+      <c r="AA338">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB338" s="7">
+      <c r="AB338">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -46548,15 +46549,15 @@
       <c r="Y339">
         <v>49</v>
       </c>
-      <c r="Z339" s="7">
+      <c r="Z339">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>47.147950000000002</v>
       </c>
-      <c r="AA339" s="7">
+      <c r="AA339">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>31.685209999999998</v>
       </c>
-      <c r="AB339" s="7">
+      <c r="AB339">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>310.41674</v>
       </c>
@@ -46645,15 +46646,15 @@
       <c r="Y340">
         <v>49</v>
       </c>
-      <c r="Z340" s="7">
+      <c r="Z340">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>36.166499999999999</v>
       </c>
-      <c r="AA340" s="7">
+      <c r="AA340">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>38.488299999999995</v>
       </c>
-      <c r="AB340" s="7">
+      <c r="AB340">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>308.79939999999999</v>
       </c>
@@ -46742,15 +46743,15 @@
       <c r="Y341">
         <v>49</v>
       </c>
-      <c r="Z341" s="7">
+      <c r="Z341">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>39.997230000000002</v>
       </c>
-      <c r="AA341" s="7">
+      <c r="AA341">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.932989999999997</v>
       </c>
-      <c r="AB341" s="7">
+      <c r="AB341">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>302.81069000000002</v>
       </c>
@@ -46839,15 +46840,15 @@
       <c r="Y342">
         <v>49</v>
       </c>
-      <c r="Z342" s="7">
+      <c r="Z342">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>30.84225</v>
       </c>
-      <c r="AA342" s="7">
+      <c r="AA342">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.488</v>
       </c>
-      <c r="AB342" s="7">
+      <c r="AB342">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>284.21775000000002</v>
       </c>
@@ -46936,15 +46937,15 @@
       <c r="Y343">
         <v>49</v>
       </c>
-      <c r="Z343" s="7">
+      <c r="Z343">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>35.906160000000007</v>
       </c>
-      <c r="AA343" s="7">
+      <c r="AA343">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>34.443690000000004</v>
       </c>
-      <c r="AB343" s="7">
+      <c r="AB343">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>333.44316000000003</v>
       </c>
@@ -47033,15 +47034,15 @@
       <c r="Y344">
         <v>49</v>
       </c>
-      <c r="Z344" s="7">
+      <c r="Z344">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA344" s="7">
+      <c r="AA344">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB344" s="7">
+      <c r="AB344">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -47130,15 +47131,15 @@
       <c r="Y345">
         <v>50</v>
       </c>
-      <c r="Z345" s="7">
+      <c r="Z345">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA345" s="7">
+      <c r="AA345">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB345" s="7">
+      <c r="AB345">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -47227,15 +47228,15 @@
       <c r="Y346">
         <v>50</v>
       </c>
-      <c r="Z346" s="7">
+      <c r="Z346">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>18.9604</v>
       </c>
-      <c r="AA346" s="7">
+      <c r="AA346">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>27.7318</v>
       </c>
-      <c r="AB346" s="7">
+      <c r="AB346">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>274.26130000000001</v>
       </c>
@@ -47324,15 +47325,15 @@
       <c r="Y347">
         <v>50</v>
       </c>
-      <c r="Z347" s="7">
+      <c r="Z347">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>37.601109999999998</v>
       </c>
-      <c r="AA347" s="7">
+      <c r="AA347">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>37.824660000000002</v>
       </c>
-      <c r="AB347" s="7">
+      <c r="AB347">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>298.84164000000004</v>
       </c>
@@ -47421,15 +47422,15 @@
       <c r="Y348">
         <v>50</v>
       </c>
-      <c r="Z348" s="7">
+      <c r="Z348">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>40.829360000000001</v>
       </c>
-      <c r="AA348" s="7">
+      <c r="AA348">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>35.19464</v>
       </c>
-      <c r="AB348" s="7">
+      <c r="AB348">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>303.24632000000003</v>
       </c>
@@ -47518,15 +47519,15 @@
       <c r="Y349">
         <v>50</v>
       </c>
-      <c r="Z349" s="7">
+      <c r="Z349">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>27.185020000000002</v>
       </c>
-      <c r="AA349" s="7">
+      <c r="AA349">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>21.192859999999996</v>
       </c>
-      <c r="AB349" s="7">
+      <c r="AB349">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>273.74478000000005</v>
       </c>
@@ -47615,15 +47616,15 @@
       <c r="Y350">
         <v>50</v>
       </c>
-      <c r="Z350" s="7">
+      <c r="Z350">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>49.461500000000001</v>
       </c>
-      <c r="AA350" s="7">
+      <c r="AA350">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>41.280250000000002</v>
       </c>
-      <c r="AB350" s="7">
+      <c r="AB350">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>326.315</v>
       </c>
@@ -47712,15 +47713,15 @@
       <c r="Y351">
         <v>50</v>
       </c>
-      <c r="Z351" s="7">
+      <c r="Z351">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA351" s="7">
+      <c r="AA351">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB351" s="7">
+      <c r="AB351">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -47809,15 +47810,15 @@
       <c r="Y352">
         <v>51</v>
       </c>
-      <c r="Z352" s="7">
+      <c r="Z352">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA352" s="7">
+      <c r="AA352">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB352" s="7">
+      <c r="AB352">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -47906,15 +47907,15 @@
       <c r="Y353">
         <v>51</v>
       </c>
-      <c r="Z353" s="7">
+      <c r="Z353">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>19.4038</v>
       </c>
-      <c r="AA353" s="7">
+      <c r="AA353">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>19.754999999999999</v>
       </c>
-      <c r="AB353" s="7">
+      <c r="AB353">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>259.75630000000001</v>
       </c>
@@ -48003,15 +48004,15 @@
       <c r="Y354">
         <v>51</v>
       </c>
-      <c r="Z354" s="7">
+      <c r="Z354">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>22.376549999999998</v>
       </c>
-      <c r="AA354" s="7">
+      <c r="AA354">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.680670000000003</v>
       </c>
-      <c r="AB354" s="7">
+      <c r="AB354">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>268.16411999999997</v>
       </c>
@@ -48100,15 +48101,15 @@
       <c r="Y355">
         <v>51</v>
       </c>
-      <c r="Z355" s="7">
+      <c r="Z355">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>32.571719999999999</v>
       </c>
-      <c r="AA355" s="7">
+      <c r="AA355">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>39.452440000000003</v>
       </c>
-      <c r="AB355" s="7">
+      <c r="AB355">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>298.86452000000003</v>
       </c>
@@ -48197,15 +48198,15 @@
       <c r="Y356">
         <v>51</v>
       </c>
-      <c r="Z356" s="7">
+      <c r="Z356">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>9.8694199999999981</v>
       </c>
-      <c r="AA356" s="7">
+      <c r="AA356">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>14.061740000000002</v>
       </c>
-      <c r="AB356" s="7">
+      <c r="AB356">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>238.00149999999999</v>
       </c>
@@ -48294,15 +48295,15 @@
       <c r="Y357">
         <v>51</v>
       </c>
-      <c r="Z357" s="7">
+      <c r="Z357">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>23.832159999999998</v>
       </c>
-      <c r="AA357" s="7">
+      <c r="AA357">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>24.767720000000001</v>
       </c>
-      <c r="AB357" s="7">
+      <c r="AB357">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>297.40959999999995</v>
       </c>
@@ -48391,15 +48392,15 @@
       <c r="Y358">
         <v>51</v>
       </c>
-      <c r="Z358" s="7">
+      <c r="Z358">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA358" s="7">
+      <c r="AA358">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB358" s="7">
+      <c r="AB358">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -48488,15 +48489,15 @@
       <c r="Y359">
         <v>52</v>
       </c>
-      <c r="Z359" s="7">
+      <c r="Z359">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA359" s="7">
+      <c r="AA359">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB359" s="7">
+      <c r="AB359">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -48585,15 +48586,15 @@
       <c r="Y360">
         <v>52</v>
       </c>
-      <c r="Z360" s="7">
+      <c r="Z360">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>26.566749999999999</v>
       </c>
-      <c r="AA360" s="7">
+      <c r="AA360">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>29.2011</v>
       </c>
-      <c r="AB360" s="7">
+      <c r="AB360">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.20650000000001</v>
       </c>
@@ -48682,15 +48683,15 @@
       <c r="Y361">
         <v>52</v>
       </c>
-      <c r="Z361" s="7">
+      <c r="Z361">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>31.13842</v>
       </c>
-      <c r="AA361" s="7">
+      <c r="AA361">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>41.221759999999996</v>
       </c>
-      <c r="AB361" s="7">
+      <c r="AB361">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>296.28140000000002</v>
       </c>
@@ -48779,15 +48780,15 @@
       <c r="Y362">
         <v>52</v>
       </c>
-      <c r="Z362" s="7">
+      <c r="Z362">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>30.52327</v>
       </c>
-      <c r="AA362" s="7">
+      <c r="AA362">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>33.159980000000004</v>
       </c>
-      <c r="AB362" s="7">
+      <c r="AB362">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>293.79205999999999</v>
       </c>
@@ -48876,15 +48877,15 @@
       <c r="Y363">
         <v>52</v>
       </c>
-      <c r="Z363" s="7">
+      <c r="Z363">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>34.397790000000001</v>
       </c>
-      <c r="AA363" s="7">
+      <c r="AA363">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>25.49952</v>
       </c>
-      <c r="AB363" s="7">
+      <c r="AB363">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>286.11700999999994</v>
       </c>
@@ -48973,15 +48974,15 @@
       <c r="Y364">
         <v>52</v>
       </c>
-      <c r="Z364" s="7">
+      <c r="Z364">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>41.315429999999999</v>
       </c>
-      <c r="AA364" s="7">
+      <c r="AA364">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>43.079789999999996</v>
       </c>
-      <c r="AB364" s="7">
+      <c r="AB364">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>333.46404000000001</v>
       </c>
@@ -49070,15 +49071,15 @@
       <c r="Y365">
         <v>52</v>
       </c>
-      <c r="Z365" s="7">
+      <c r="Z365">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_grasa_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AA365" s="7">
+      <c r="AA365">
         <f>Tabla1[[#This Row],[suero_litros]]*Tabla1[[#This Row],[suero_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="AB365" s="7">
+      <c r="AB365">
         <f>Tabla1[[#This Row],[suero_est_g_l]]*Tabla1[[#This Row],[suero_litros]]/1000</f>
         <v>0</v>
       </c>
@@ -49134,13 +49135,13 @@
       <c r="C4" s="4">
         <v>0</v>
       </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>0</v>
       </c>
     </row>
@@ -49154,13 +49155,13 @@
       <c r="C5" s="4">
         <v>52907.247520000004</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5">
         <v>163268.71</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>44117.928741000003</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5">
         <v>8615.4818200000027</v>
       </c>
     </row>
@@ -49174,13 +49175,13 @@
       <c r="C6" s="4">
         <v>4681.7112899999993</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6">
         <v>14431.04</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6">
         <v>3917.9846070000003</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6">
         <v>750.10509000000002</v>
       </c>
     </row>
@@ -49194,13 +49195,13 @@
       <c r="C7" s="4">
         <v>4330.8305199999986</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7">
         <v>13159.799999999997</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <v>3576.0024059999996</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7">
         <v>740.37126000000012</v>
       </c>
     </row>
@@ -49214,13 +49215,13 @@
       <c r="C8" s="4">
         <v>4238.1888399999998</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8">
         <v>13041.910000000002</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <v>3524.5914470000002</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8">
         <v>697.08172999999999</v>
       </c>
     </row>
@@ -49234,13 +49235,13 @@
       <c r="C9" s="4">
         <v>4446.4499800000003</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9">
         <v>13805.960000000001</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9">
         <v>3732.4897259999998</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9">
         <v>699.20452999999998</v>
       </c>
     </row>
@@ -49254,13 +49255,13 @@
       <c r="C10" s="4">
         <v>4619.3823799999991</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10">
         <v>14378.560000000001</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10">
         <v>3890.9175639999994</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10">
         <v>714.85093999999992</v>
       </c>
     </row>
@@ -49274,13 +49275,13 @@
       <c r="C11" s="4">
         <v>4057.5834600000003</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11">
         <v>12588.75</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11">
         <v>3368.5918529999999</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11">
         <v>674.64871000000016</v>
       </c>
     </row>
@@ -49294,13 +49295,13 @@
       <c r="C12" s="4">
         <v>4551.9588699999995</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12">
         <v>14246.809999999998</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12">
         <v>3830.821903</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12">
         <v>705.13085999999998</v>
       </c>
     </row>
@@ -49314,13 +49315,13 @@
       <c r="C13" s="4">
         <v>4516.0359099999996</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13">
         <v>13667.88</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13">
         <v>3678.4507409999997</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13">
         <v>821.44869000000006</v>
       </c>
     </row>
@@ -49334,13 +49335,13 @@
       <c r="C14" s="4">
         <v>4314.8450599999996</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14">
         <v>13267.100000000002</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14">
         <v>3590.7186140000003</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14">
         <v>709.99793</v>
       </c>
     </row>
@@ -49354,13 +49355,13 @@
       <c r="C15" s="4">
         <v>4759.3344899999993</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15">
         <v>14778.189999999999</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15">
         <v>3979.1869849999998</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15">
         <v>765.40995000000009</v>
       </c>
     </row>
@@ -49374,13 +49375,13 @@
       <c r="C16" s="4">
         <v>4281.0841199999995</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16">
         <v>13185.469999999998</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16">
         <v>3567.0441490000003</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16">
         <v>701.13934000000017</v>
       </c>
     </row>
@@ -49394,13 +49395,13 @@
       <c r="C17" s="4">
         <v>4109.8425999999999</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17">
         <v>12717.24</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17">
         <v>3461.1287460000003</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17">
         <v>636.09279000000004</v>
       </c>
     </row>
@@ -49414,13 +49415,13 @@
       <c r="C18" s="4">
         <v>52907.247520000004</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18">
         <v>163268.71</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18">
         <v>44117.928741000003</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18">
         <v>8615.4818200000027</v>
       </c>
       <c r="G18" s="4"/>
@@ -49433,7 +49434,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69177222-3497-46B6-96D5-F4D0CF35476B}">
-  <dimension ref="A3:F18"/>
+  <dimension ref="A3:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -49474,13 +49475,13 @@
       <c r="C4" s="4">
         <v>0</v>
       </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>0</v>
       </c>
     </row>
@@ -49494,13 +49495,13 @@
       <c r="C5" s="4">
         <v>44658.931230000002</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5">
         <v>163268.71</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>40756.398627000002</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5">
         <v>6932.9705499999982</v>
       </c>
     </row>
@@ -49514,13 +49515,13 @@
       <c r="C6" s="4">
         <v>3958.4646100000009</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6">
         <v>14431.04</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6">
         <v>3584.8440320000004</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6">
         <v>610.88019999999995</v>
       </c>
     </row>
@@ -49534,13 +49535,13 @@
       <c r="C7" s="4">
         <v>3616.1289500000003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7">
         <v>13159.799999999997</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <v>3285.9229610000007</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7">
         <v>572.31288999999992</v>
       </c>
     </row>
@@ -49554,13 +49555,13 @@
       <c r="C8" s="4">
         <v>3548.1611199999998</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8">
         <v>13041.910000000002</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <v>3233.7174000000005</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8">
         <v>535.52634</v>
       </c>
     </row>
@@ -49574,13 +49575,13 @@
       <c r="C9" s="4">
         <v>3838.8228099999997</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9">
         <v>13805.960000000001</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9">
         <v>3455.5167520000009</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9">
         <v>660.32703000000004</v>
       </c>
     </row>
@@ -49594,13 +49595,13 @@
       <c r="C10" s="4">
         <v>3911.9241999999999</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10">
         <v>14378.560000000001</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10">
         <v>3583.8960970000003</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10">
         <v>580.17899999999997</v>
       </c>
     </row>
@@ -49614,13 +49615,13 @@
       <c r="C11" s="4">
         <v>3373.5486199999991</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11">
         <v>12588.75</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11">
         <v>3137.8367779999999</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11">
         <v>452.85509000000002</v>
       </c>
     </row>
@@ -49634,13 +49635,13 @@
       <c r="C12" s="4">
         <v>3873.5423600000004</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12">
         <v>14246.809999999998</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12">
         <v>3545.1011620000008</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12">
         <v>594.49404000000004</v>
       </c>
     </row>
@@ -49654,13 +49655,13 @@
       <c r="C13" s="4">
         <v>3793.9515000000001</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13">
         <v>13667.88</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13">
         <v>3445.8885109999997</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13">
         <v>618.66466000000003</v>
       </c>
     </row>
@@ -49674,13 +49675,13 @@
       <c r="C14" s="4">
         <v>3630.4452200000001</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14">
         <v>13267.100000000002</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14">
         <v>3311.7427200000011</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14">
         <v>560.78108999999995</v>
       </c>
     </row>
@@ -49694,13 +49695,13 @@
       <c r="C15" s="4">
         <v>3983.1665700000003</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15">
         <v>14778.189999999999</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15">
         <v>3707.1614600000003</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15">
         <v>567.85068000000001</v>
       </c>
     </row>
@@ -49714,17 +49715,17 @@
       <c r="C16" s="4">
         <v>3600.2601299999997</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16">
         <v>13185.469999999998</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16">
         <v>3267.7563109999992</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16">
         <v>556.95740999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
@@ -49734,17 +49735,17 @@
       <c r="C17" s="4">
         <v>3530.5151400000004</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17">
         <v>12717.24</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17">
         <v>3197.0144430000005</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17">
         <v>622.14211999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>21</v>
       </c>
@@ -49754,15 +49755,16 @@
       <c r="C18" s="4">
         <v>44658.931230000002</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18">
         <v>163268.71</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18">
         <v>40756.398627000002</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18">
         <v>6932.9705499999982</v>
       </c>
+      <c r="H18" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
